--- a/estadistica2/data/droguett_sepulveda.xlsx
+++ b/estadistica2/data/droguett_sepulveda.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kennethbunker/Library/CloudStorage/Dropbox/GitHub/uss/estadistica2/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1E600AF-BF23-084A-9F84-74D08072AE05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BFEA2DEF-3EC1-3543-9D2F-E5CFF4FC8656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="3" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">codebook!$A$1:$E$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$S$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$R$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="90">
   <si>
     <t>date</t>
   </si>
@@ -305,6 +305,12 @@
   <si>
     <t>yyyy-mm-dd</t>
   </si>
+  <si>
+    <t>fecha eleccion</t>
+  </si>
+  <si>
+    <t>dias transcurridos</t>
+  </si>
 </sst>
 </file>
 
@@ -416,14 +422,14 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -738,14 +744,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83B63D74-A7C5-D44D-829C-4061152A24B6}">
-  <dimension ref="A1:S210"/>
+  <dimension ref="A1:R210"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.1640625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="10.1640625" style="15" customWidth="1"/>
+    <col min="3" max="3" width="10.1640625" style="17" customWidth="1"/>
     <col min="4" max="4" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.1640625" style="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.1640625" style="14" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.83203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.1640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.33203125" bestFit="1" customWidth="1"/>
@@ -758,24 +764,23 @@
     <col min="15" max="15" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.5" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.33203125" customWidth="1"/>
+    <col min="18" max="18" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="13" t="s">
         <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -815,27 +820,24 @@
         <v>73</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="S1" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>44505</v>
       </c>
       <c r="B2" s="4">
         <v>44517</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="17">
         <f>B2-A2</f>
         <v>12</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="17">
+      <c r="E2" s="14">
         <v>2352</v>
       </c>
       <c r="F2" t="s">
@@ -848,7 +850,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="11">
-        <f>28-J2</f>
+        <f>ABS(28-J2)</f>
         <v>6.3000000000000007</v>
       </c>
       <c r="J2" s="2">
@@ -875,25 +877,25 @@
       <c r="Q2" s="2">
         <v>19.7</v>
       </c>
-      <c r="S2" t="s">
+      <c r="R2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>44505</v>
       </c>
       <c r="B3" s="4">
-        <v>44518</v>
-      </c>
-      <c r="C3" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C3" s="17">
         <f t="shared" ref="C3:C66" si="0">B3-A3</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="17">
+      <c r="E3" s="14">
         <v>1349</v>
       </c>
       <c r="F3" t="s">
@@ -906,7 +908,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="11">
-        <f t="shared" ref="I3:I66" si="1">28-J3</f>
+        <f t="shared" ref="I3:I66" si="1">ABS(28-J3)</f>
         <v>0.69999999999999929</v>
       </c>
       <c r="J3" s="2">
@@ -933,25 +935,25 @@
       <c r="Q3" s="2">
         <v>7.5</v>
       </c>
-      <c r="S3" t="s">
+      <c r="R3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>44504</v>
       </c>
       <c r="B4" s="4">
-        <v>44519</v>
-      </c>
-      <c r="C4" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C4" s="17">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="14">
         <v>1010</v>
       </c>
       <c r="F4" t="s">
@@ -991,25 +993,25 @@
       <c r="Q4" s="2">
         <v>22</v>
       </c>
-      <c r="S4" t="s">
+      <c r="R4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>44504</v>
       </c>
       <c r="B5" s="4">
-        <v>44520</v>
-      </c>
-      <c r="C5" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C5" s="17">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="14">
         <v>100</v>
       </c>
       <c r="F5" t="s">
@@ -1023,7 +1025,7 @@
       </c>
       <c r="I5" s="11">
         <f t="shared" si="1"/>
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="J5" s="2">
         <v>32</v>
@@ -1049,25 +1051,25 @@
       <c r="Q5" s="2">
         <v>0</v>
       </c>
-      <c r="S5" t="s">
+      <c r="R5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>44503</v>
       </c>
       <c r="B6" s="4">
-        <v>44521</v>
-      </c>
-      <c r="C6" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C6" s="17">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="14">
         <v>7613</v>
       </c>
       <c r="F6" t="s">
@@ -1107,25 +1109,25 @@
       <c r="Q6" s="2">
         <v>17</v>
       </c>
-      <c r="S6" t="s">
+      <c r="R6" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>44502</v>
       </c>
       <c r="B7" s="4">
-        <v>44522</v>
-      </c>
-      <c r="C7" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C7" s="17">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="14">
         <v>2266</v>
       </c>
       <c r="F7" t="s">
@@ -1139,7 +1141,7 @@
       </c>
       <c r="I7" s="11">
         <f t="shared" si="1"/>
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="J7" s="2">
         <v>31</v>
@@ -1165,25 +1167,25 @@
       <c r="Q7" s="2">
         <v>6.6</v>
       </c>
-      <c r="S7" t="s">
+      <c r="R7" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>44502</v>
       </c>
       <c r="B8" s="4">
-        <v>44523</v>
-      </c>
-      <c r="C8" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C8" s="17">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="14">
         <v>2266</v>
       </c>
       <c r="F8" t="s">
@@ -1197,7 +1199,7 @@
       </c>
       <c r="I8" s="11">
         <f t="shared" si="1"/>
-        <v>-6.2000000000000028</v>
+        <v>6.2000000000000028</v>
       </c>
       <c r="J8" s="2">
         <v>34.200000000000003</v>
@@ -1221,25 +1223,25 @@
         <v>2.7</v>
       </c>
       <c r="Q8" s="2"/>
-      <c r="S8" t="s">
+      <c r="R8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>44502</v>
       </c>
       <c r="B9" s="4">
-        <v>44524</v>
-      </c>
-      <c r="C9" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C9" s="17">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="14">
         <v>1523</v>
       </c>
       <c r="F9" t="s">
@@ -1279,25 +1281,25 @@
       <c r="Q9" s="2">
         <v>19</v>
       </c>
-      <c r="S9" t="s">
+      <c r="R9" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>44502</v>
       </c>
       <c r="B10" s="4">
-        <v>44525</v>
-      </c>
-      <c r="C10" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C10" s="17">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D10" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="14">
         <v>2430</v>
       </c>
       <c r="F10" t="s">
@@ -1311,7 +1313,7 @@
       </c>
       <c r="I10" s="11">
         <f t="shared" si="1"/>
-        <v>-8</v>
+        <v>8</v>
       </c>
       <c r="J10" s="2">
         <v>36</v>
@@ -1337,25 +1339,25 @@
       <c r="Q10" s="2">
         <v>2</v>
       </c>
-      <c r="S10" t="s">
+      <c r="R10" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>44502</v>
       </c>
       <c r="B11" s="4">
-        <v>44526</v>
-      </c>
-      <c r="C11" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C11" s="17">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="14">
         <v>5064</v>
       </c>
       <c r="F11" t="s">
@@ -1369,7 +1371,7 @@
       </c>
       <c r="I11" s="11">
         <f t="shared" si="1"/>
-        <v>-11</v>
+        <v>11</v>
       </c>
       <c r="J11" s="2">
         <v>39</v>
@@ -1393,25 +1395,25 @@
         <v>2</v>
       </c>
       <c r="Q11" s="2"/>
-      <c r="S11" t="s">
+      <c r="R11" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>44500</v>
       </c>
       <c r="B12" s="4">
-        <v>44527</v>
-      </c>
-      <c r="C12" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C12" s="17">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D12" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="14">
         <v>1743</v>
       </c>
       <c r="F12" t="s">
@@ -1451,25 +1453,25 @@
       <c r="Q12" s="2">
         <v>5</v>
       </c>
-      <c r="S12" t="s">
+      <c r="R12" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>44500</v>
       </c>
       <c r="B13" s="4">
-        <v>44528</v>
-      </c>
-      <c r="C13" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C13" s="17">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="14">
         <v>100</v>
       </c>
       <c r="F13" t="s">
@@ -1507,25 +1509,25 @@
         <v>2</v>
       </c>
       <c r="Q13" s="2"/>
-      <c r="S13" t="s">
+      <c r="R13" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>44500</v>
       </c>
       <c r="B14" s="4">
-        <v>44529</v>
-      </c>
-      <c r="C14" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C14" s="17">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="14">
         <v>1493</v>
       </c>
       <c r="F14" t="s">
@@ -1539,7 +1541,7 @@
       </c>
       <c r="I14" s="11">
         <f t="shared" si="1"/>
-        <v>-9.8999999999999986</v>
+        <v>9.8999999999999986</v>
       </c>
       <c r="J14" s="2">
         <v>37.9</v>
@@ -1563,25 +1565,25 @@
         <v>1.9</v>
       </c>
       <c r="Q14" s="2"/>
-      <c r="S14" t="s">
+      <c r="R14" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>44498</v>
       </c>
       <c r="B15" s="4">
-        <v>44530</v>
-      </c>
-      <c r="C15" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C15" s="17">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D15" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="14">
         <v>2027</v>
       </c>
       <c r="F15" t="s">
@@ -1621,25 +1623,25 @@
       <c r="Q15" s="2">
         <v>22.4</v>
       </c>
-      <c r="S15" t="s">
+      <c r="R15" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>44498</v>
       </c>
       <c r="B16" s="4">
-        <v>44531</v>
-      </c>
-      <c r="C16" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C16" s="17">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D16" t="s">
         <v>10</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="14">
         <v>1110</v>
       </c>
       <c r="F16" t="s">
@@ -1679,25 +1681,25 @@
       <c r="Q16" s="2">
         <v>8.8000000000000007</v>
       </c>
-      <c r="S16" t="s">
+      <c r="R16" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>44498</v>
       </c>
       <c r="B17" s="4">
-        <v>44532</v>
-      </c>
-      <c r="C17" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C17" s="17">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D17" t="s">
         <v>2</v>
       </c>
-      <c r="E17" s="17">
+      <c r="E17" s="14">
         <v>1005</v>
       </c>
       <c r="F17" t="s">
@@ -1737,25 +1739,25 @@
       <c r="Q17" s="2">
         <v>26</v>
       </c>
-      <c r="S17" t="s">
+      <c r="R17" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>44498</v>
       </c>
       <c r="B18" s="4">
-        <v>44533</v>
-      </c>
-      <c r="C18" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C18" s="17">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s">
         <v>2</v>
       </c>
-      <c r="E18" s="17">
+      <c r="E18" s="14">
         <v>100</v>
       </c>
       <c r="F18" t="s">
@@ -1769,7 +1771,7 @@
       </c>
       <c r="I18" s="11">
         <f t="shared" si="1"/>
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="J18" s="2">
         <v>32</v>
@@ -1793,25 +1795,25 @@
         <v>1</v>
       </c>
       <c r="Q18" s="2"/>
-      <c r="S18" t="s">
+      <c r="R18" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>44495</v>
       </c>
       <c r="B19" s="4">
-        <v>44534</v>
-      </c>
-      <c r="C19" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C19" s="17">
         <f t="shared" si="0"/>
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="D19" t="s">
         <v>39</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="14">
         <v>600</v>
       </c>
       <c r="F19" t="s">
@@ -1825,7 +1827,7 @@
       </c>
       <c r="I19" s="11">
         <f t="shared" si="1"/>
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="J19" s="2">
         <v>30</v>
@@ -1850,21 +1852,21 @@
       </c>
       <c r="Q19" s="2"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>44491</v>
       </c>
       <c r="B20" s="4">
-        <v>44535</v>
-      </c>
-      <c r="C20" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C20" s="17">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="D20" t="s">
         <v>2</v>
       </c>
-      <c r="E20" s="17">
+      <c r="E20" s="14">
         <v>1007</v>
       </c>
       <c r="F20" t="s">
@@ -1904,25 +1906,25 @@
       <c r="Q20" s="2">
         <v>26</v>
       </c>
-      <c r="S20" t="s">
+      <c r="R20" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>44491</v>
       </c>
       <c r="B21" s="4">
-        <v>44536</v>
-      </c>
-      <c r="C21" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C21" s="17">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="D21" t="s">
         <v>2</v>
       </c>
-      <c r="E21" s="17">
+      <c r="E21" s="14">
         <v>100</v>
       </c>
       <c r="F21" t="s">
@@ -1936,7 +1938,7 @@
       </c>
       <c r="I21" s="11">
         <f t="shared" si="1"/>
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="J21" s="2">
         <v>31</v>
@@ -1962,25 +1964,25 @@
       <c r="Q21" s="2">
         <v>0</v>
       </c>
-      <c r="S21" t="s">
+      <c r="R21" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>44491</v>
       </c>
       <c r="B22" s="4">
-        <v>44537</v>
-      </c>
-      <c r="C22" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C22" s="17">
         <f t="shared" si="0"/>
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="D22" t="s">
         <v>9</v>
       </c>
-      <c r="E22" s="17">
+      <c r="E22" s="14">
         <v>1118</v>
       </c>
       <c r="F22" t="s">
@@ -2019,21 +2021,21 @@
       </c>
       <c r="Q22" s="2"/>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>44484</v>
       </c>
       <c r="B23" s="4">
-        <v>44538</v>
-      </c>
-      <c r="C23" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C23" s="17">
         <f t="shared" si="0"/>
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="D23" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="14">
         <v>1632</v>
       </c>
       <c r="F23" t="s">
@@ -2073,25 +2075,25 @@
       <c r="Q23" s="2">
         <v>21.6</v>
       </c>
-      <c r="S23" t="s">
+      <c r="R23" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>44484</v>
       </c>
       <c r="B24" s="4">
-        <v>44539</v>
-      </c>
-      <c r="C24" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C24" s="17">
         <f t="shared" si="0"/>
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="D24" t="s">
         <v>10</v>
       </c>
-      <c r="E24" s="17">
+      <c r="E24" s="14">
         <v>901</v>
       </c>
       <c r="F24" t="s">
@@ -2131,25 +2133,25 @@
       <c r="Q24" s="2">
         <v>9.8000000000000007</v>
       </c>
-      <c r="S24" t="s">
+      <c r="R24" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>44483</v>
       </c>
       <c r="B25" s="4">
-        <v>44540</v>
-      </c>
-      <c r="C25" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C25" s="17">
         <f t="shared" si="0"/>
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="D25" t="s">
         <v>2</v>
       </c>
-      <c r="E25" s="17">
+      <c r="E25" s="14">
         <v>706</v>
       </c>
       <c r="F25" t="s">
@@ -2189,25 +2191,25 @@
       <c r="Q25" s="2">
         <v>27</v>
       </c>
-      <c r="S25" t="s">
+      <c r="R25" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>44483</v>
       </c>
       <c r="B26" s="4">
-        <v>44541</v>
-      </c>
-      <c r="C26" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C26" s="17">
         <f t="shared" si="0"/>
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="D26" t="s">
         <v>2</v>
       </c>
-      <c r="E26" s="17">
+      <c r="E26" s="14">
         <v>100</v>
       </c>
       <c r="F26" t="s">
@@ -2221,7 +2223,7 @@
       </c>
       <c r="I26" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J26" s="2">
         <v>29</v>
@@ -2247,25 +2249,25 @@
       <c r="Q26" s="2">
         <v>0</v>
       </c>
-      <c r="S26" t="s">
+      <c r="R26" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>44477</v>
       </c>
       <c r="B27" s="4">
-        <v>44542</v>
-      </c>
-      <c r="C27" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C27" s="17">
         <f t="shared" si="0"/>
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="D27" t="s">
         <v>2</v>
       </c>
-      <c r="E27" s="17">
+      <c r="E27" s="14">
         <v>704</v>
       </c>
       <c r="F27" t="s">
@@ -2305,25 +2307,25 @@
       <c r="Q27" s="2">
         <v>27</v>
       </c>
-      <c r="S27" t="s">
+      <c r="R27" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>44477</v>
       </c>
       <c r="B28" s="4">
-        <v>44543</v>
-      </c>
-      <c r="C28" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C28" s="17">
         <f t="shared" si="0"/>
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="D28" t="s">
         <v>2</v>
       </c>
-      <c r="E28" s="17">
+      <c r="E28" s="14">
         <v>100</v>
       </c>
       <c r="F28" t="s">
@@ -2363,25 +2365,25 @@
       <c r="Q28" s="2">
         <v>0</v>
       </c>
-      <c r="S28" t="s">
+      <c r="R28" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>44476</v>
       </c>
       <c r="B29" s="4">
-        <v>44544</v>
-      </c>
-      <c r="C29" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C29" s="17">
         <f t="shared" si="0"/>
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="D29" t="s">
         <v>42</v>
       </c>
-      <c r="E29" s="17">
+      <c r="E29" s="14">
         <v>5011</v>
       </c>
       <c r="F29" t="s">
@@ -2419,25 +2421,25 @@
         <v>2</v>
       </c>
       <c r="Q29" s="2"/>
-      <c r="S29" t="s">
+      <c r="R29" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>44474</v>
       </c>
       <c r="B30" s="4">
-        <v>44545</v>
-      </c>
-      <c r="C30" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C30" s="17">
         <f t="shared" si="0"/>
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="D30" t="s">
         <v>9</v>
       </c>
-      <c r="E30" s="17">
+      <c r="E30" s="14">
         <v>1485</v>
       </c>
       <c r="F30" t="s">
@@ -2477,25 +2479,25 @@
       <c r="Q30" s="2">
         <v>14</v>
       </c>
-      <c r="S30" t="s">
+      <c r="R30" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>44473</v>
       </c>
       <c r="B31" s="4">
-        <v>44546</v>
-      </c>
-      <c r="C31" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C31" s="17">
         <f t="shared" si="0"/>
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="D31" t="s">
         <v>7</v>
       </c>
-      <c r="E31" s="17">
+      <c r="E31" s="14">
         <v>1446</v>
       </c>
       <c r="F31" t="s">
@@ -2535,25 +2537,25 @@
       <c r="Q31" s="2">
         <v>19</v>
       </c>
-      <c r="S31" t="s">
+      <c r="R31" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>44470</v>
       </c>
       <c r="B32" s="4">
-        <v>44547</v>
-      </c>
-      <c r="C32" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C32" s="17">
         <f t="shared" si="0"/>
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="D32" t="s">
         <v>10</v>
       </c>
-      <c r="E32" s="17">
+      <c r="E32" s="14">
         <v>1601</v>
       </c>
       <c r="F32" t="s">
@@ -2593,25 +2595,25 @@
       <c r="Q32" s="2">
         <v>24</v>
       </c>
-      <c r="S32" t="s">
+      <c r="R32" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>44470</v>
       </c>
       <c r="B33" s="4">
-        <v>44548</v>
-      </c>
-      <c r="C33" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C33" s="17">
         <f t="shared" si="0"/>
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="D33" t="s">
         <v>10</v>
       </c>
-      <c r="E33" s="17">
+      <c r="E33" s="14">
         <v>878</v>
       </c>
       <c r="F33" t="s">
@@ -2651,25 +2653,25 @@
       <c r="Q33" s="2">
         <v>13.8</v>
       </c>
-      <c r="S33" t="s">
+      <c r="R33" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>44470</v>
       </c>
       <c r="B34" s="4">
-        <v>44549</v>
-      </c>
-      <c r="C34" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C34" s="17">
         <f t="shared" si="0"/>
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="D34" t="s">
         <v>2</v>
       </c>
-      <c r="E34" s="17">
+      <c r="E34" s="14">
         <v>705</v>
       </c>
       <c r="F34" t="s">
@@ -2709,25 +2711,25 @@
       <c r="Q34" s="2">
         <v>28</v>
       </c>
-      <c r="S34" t="s">
+      <c r="R34" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>44470</v>
       </c>
       <c r="B35" s="4">
-        <v>44550</v>
-      </c>
-      <c r="C35" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C35" s="17">
         <f t="shared" si="0"/>
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="D35" t="s">
         <v>2</v>
       </c>
-      <c r="E35" s="17">
+      <c r="E35" s="14">
         <v>100</v>
       </c>
       <c r="F35" t="s">
@@ -2767,25 +2769,25 @@
       <c r="Q35" s="2">
         <v>0</v>
       </c>
-      <c r="S35" t="s">
+      <c r="R35" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>44463</v>
       </c>
       <c r="B36" s="4">
-        <v>44551</v>
-      </c>
-      <c r="C36" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C36" s="17">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="D36" t="s">
         <v>2</v>
       </c>
-      <c r="E36" s="17">
+      <c r="E36" s="14">
         <v>703</v>
       </c>
       <c r="F36" t="s">
@@ -2825,25 +2827,25 @@
       <c r="Q36" s="2">
         <v>26</v>
       </c>
-      <c r="S36" t="s">
+      <c r="R36" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>44463</v>
       </c>
       <c r="B37" s="4">
-        <v>44552</v>
-      </c>
-      <c r="C37" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C37" s="17">
         <f t="shared" si="0"/>
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="D37" t="s">
         <v>2</v>
       </c>
-      <c r="E37" s="17">
+      <c r="E37" s="14">
         <v>100</v>
       </c>
       <c r="F37" t="s">
@@ -2883,25 +2885,25 @@
       <c r="Q37" s="2">
         <v>0</v>
       </c>
-      <c r="S37" t="s">
+      <c r="R37" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>44463</v>
       </c>
       <c r="B38" s="4">
-        <v>44553</v>
-      </c>
-      <c r="C38" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C38" s="17">
         <f t="shared" si="0"/>
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="D38" t="s">
         <v>42</v>
       </c>
-      <c r="E38" s="17">
+      <c r="E38" s="14">
         <v>944</v>
       </c>
       <c r="F38" t="s">
@@ -2941,25 +2943,25 @@
       <c r="Q38" s="2">
         <v>26</v>
       </c>
-      <c r="S38" t="s">
+      <c r="R38" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>44455</v>
       </c>
       <c r="B39" s="4">
-        <v>44554</v>
-      </c>
-      <c r="C39" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C39" s="17">
         <f t="shared" si="0"/>
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="D39" t="s">
         <v>2</v>
       </c>
-      <c r="E39" s="17">
+      <c r="E39" s="14">
         <v>709</v>
       </c>
       <c r="F39" t="s">
@@ -2999,25 +3001,25 @@
       <c r="Q39" s="2">
         <v>27</v>
       </c>
-      <c r="S39" t="s">
+      <c r="R39" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>44455</v>
       </c>
       <c r="B40" s="4">
-        <v>44555</v>
-      </c>
-      <c r="C40" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C40" s="17">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="D40" t="s">
         <v>2</v>
       </c>
-      <c r="E40" s="17">
+      <c r="E40" s="14">
         <v>100</v>
       </c>
       <c r="F40" t="s">
@@ -3057,25 +3059,25 @@
       <c r="Q40" s="2">
         <v>0</v>
       </c>
-      <c r="S40" t="s">
+      <c r="R40" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
         <v>44453</v>
       </c>
       <c r="B41" s="4">
-        <v>44556</v>
-      </c>
-      <c r="C41" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C41" s="17">
         <f t="shared" si="0"/>
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="D41" t="s">
         <v>39</v>
       </c>
-      <c r="E41" s="17">
+      <c r="E41" s="14">
         <v>600</v>
       </c>
       <c r="F41" t="s">
@@ -3115,25 +3117,25 @@
       <c r="Q41" s="2">
         <v>0</v>
       </c>
-      <c r="S41" t="s">
+      <c r="R41" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
         <v>44449</v>
       </c>
       <c r="B42" s="4">
-        <v>44557</v>
-      </c>
-      <c r="C42" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C42" s="17">
         <f t="shared" si="0"/>
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="D42" t="s">
         <v>2</v>
       </c>
-      <c r="E42" s="17">
+      <c r="E42" s="14">
         <v>705</v>
       </c>
       <c r="F42" t="s">
@@ -3171,25 +3173,25 @@
       <c r="Q42" s="2">
         <v>29</v>
       </c>
-      <c r="S42" t="s">
+      <c r="R42" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
         <v>44445</v>
       </c>
       <c r="B43" s="4">
-        <v>44558</v>
-      </c>
-      <c r="C43" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C43" s="17">
         <f t="shared" si="0"/>
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
       </c>
-      <c r="E43" s="17">
+      <c r="E43" s="14">
         <v>1619</v>
       </c>
       <c r="F43" t="s">
@@ -3229,25 +3231,25 @@
       <c r="Q43" s="2">
         <v>13.9</v>
       </c>
-      <c r="S43" t="s">
+      <c r="R43" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
         <v>44442</v>
       </c>
       <c r="B44" s="4">
-        <v>44559</v>
-      </c>
-      <c r="C44" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C44" s="17">
         <f t="shared" si="0"/>
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="D44" t="s">
         <v>2</v>
       </c>
-      <c r="E44" s="17">
+      <c r="E44" s="14">
         <v>702</v>
       </c>
       <c r="F44" t="s">
@@ -3285,25 +3287,25 @@
       <c r="Q44" s="2">
         <v>25</v>
       </c>
-      <c r="S44" t="s">
+      <c r="R44" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
         <v>44440</v>
       </c>
       <c r="B45" s="4">
-        <v>44560</v>
-      </c>
-      <c r="C45" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C45" s="17">
         <f t="shared" si="0"/>
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="D45" t="s">
         <v>35</v>
       </c>
-      <c r="E45" s="17">
+      <c r="E45" s="14">
         <v>1443</v>
       </c>
       <c r="F45" t="s">
@@ -3339,25 +3341,25 @@
       <c r="Q45" s="2">
         <v>50</v>
       </c>
-      <c r="S45" t="s">
+      <c r="R45" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
         <v>44439</v>
       </c>
       <c r="B46" s="4">
-        <v>44561</v>
-      </c>
-      <c r="C46" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C46" s="17">
         <f t="shared" si="0"/>
-        <v>122</v>
+        <v>78</v>
       </c>
       <c r="D46" t="s">
         <v>9</v>
       </c>
-      <c r="E46" s="17">
+      <c r="E46" s="14">
         <v>1551</v>
       </c>
       <c r="F46" t="s">
@@ -3397,25 +3399,25 @@
       <c r="Q46" s="2">
         <v>14</v>
       </c>
-      <c r="S46" t="s">
+      <c r="R46" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A47" s="4">
         <v>44435</v>
       </c>
       <c r="B47" s="4">
-        <v>44562</v>
-      </c>
-      <c r="C47" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C47" s="17">
         <f t="shared" si="0"/>
-        <v>127</v>
+        <v>82</v>
       </c>
       <c r="D47" t="s">
         <v>10</v>
       </c>
-      <c r="E47" s="17">
+      <c r="E47" s="14">
         <v>1559</v>
       </c>
       <c r="F47" t="s">
@@ -3455,25 +3457,25 @@
       <c r="Q47" s="2">
         <v>24.6</v>
       </c>
-      <c r="S47" t="s">
+      <c r="R47" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
         <v>44435</v>
       </c>
       <c r="B48" s="4">
-        <v>44563</v>
-      </c>
-      <c r="C48" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C48" s="17">
         <f t="shared" si="0"/>
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="D48" t="s">
         <v>10</v>
       </c>
-      <c r="E48" s="17">
+      <c r="E48" s="14">
         <v>967</v>
       </c>
       <c r="F48" t="s">
@@ -3513,25 +3515,25 @@
       <c r="Q48" s="2">
         <v>20.399999999999999</v>
       </c>
-      <c r="S48" t="s">
+      <c r="R48" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
         <v>44435</v>
       </c>
       <c r="B49" s="4">
-        <v>44564</v>
-      </c>
-      <c r="C49" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C49" s="17">
         <f t="shared" si="0"/>
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="D49" t="s">
         <v>2</v>
       </c>
-      <c r="E49" s="17">
+      <c r="E49" s="14">
         <v>704</v>
       </c>
       <c r="F49" t="s">
@@ -3571,25 +3573,25 @@
       <c r="Q49" s="2">
         <v>26</v>
       </c>
-      <c r="S49" t="s">
+      <c r="R49" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
         <v>44421</v>
       </c>
       <c r="B50" s="4">
-        <v>44565</v>
-      </c>
-      <c r="C50" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C50" s="17">
         <f t="shared" si="0"/>
-        <v>144</v>
+        <v>96</v>
       </c>
       <c r="D50" t="s">
         <v>10</v>
       </c>
-      <c r="E50" s="17">
+      <c r="E50" s="14">
         <v>1410</v>
       </c>
       <c r="F50" t="s">
@@ -3629,25 +3631,25 @@
       <c r="Q50" s="2">
         <v>22.2</v>
       </c>
-      <c r="S50" t="s">
+      <c r="R50" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
         <v>44421</v>
       </c>
       <c r="B51" s="4">
-        <v>44566</v>
-      </c>
-      <c r="C51" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C51" s="17">
         <f t="shared" si="0"/>
-        <v>145</v>
+        <v>96</v>
       </c>
       <c r="D51" t="s">
         <v>10</v>
       </c>
-      <c r="E51" s="17">
+      <c r="E51" s="14">
         <v>890</v>
       </c>
       <c r="F51" t="s">
@@ -3687,25 +3689,25 @@
       <c r="Q51" s="2">
         <v>20.399999999999999</v>
       </c>
-      <c r="S51" t="s">
+      <c r="R51" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
         <v>44421</v>
       </c>
       <c r="B52" s="4">
-        <v>44567</v>
-      </c>
-      <c r="C52" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C52" s="17">
         <f t="shared" si="0"/>
-        <v>146</v>
+        <v>96</v>
       </c>
       <c r="D52" t="s">
         <v>2</v>
       </c>
-      <c r="E52" s="17">
+      <c r="E52" s="14">
         <v>703</v>
       </c>
       <c r="F52" t="s">
@@ -3739,25 +3741,25 @@
       <c r="Q52" s="2">
         <v>29</v>
       </c>
-      <c r="S52" t="s">
+      <c r="R52" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
         <v>44414</v>
       </c>
       <c r="B53" s="4">
-        <v>44568</v>
-      </c>
-      <c r="C53" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C53" s="17">
         <f t="shared" si="0"/>
-        <v>154</v>
+        <v>103</v>
       </c>
       <c r="D53" t="s">
         <v>2</v>
       </c>
-      <c r="E53" s="17">
+      <c r="E53" s="14">
         <v>702</v>
       </c>
       <c r="F53" t="s">
@@ -3791,25 +3793,25 @@
       <c r="Q53" s="2">
         <v>28</v>
       </c>
-      <c r="S53" t="s">
+      <c r="R53" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
         <v>44411</v>
       </c>
       <c r="B54" s="4">
-        <v>44569</v>
-      </c>
-      <c r="C54" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C54" s="17">
         <f t="shared" si="0"/>
-        <v>158</v>
+        <v>106</v>
       </c>
       <c r="D54" t="s">
         <v>9</v>
       </c>
-      <c r="E54" s="17">
+      <c r="E54" s="14">
         <v>1026</v>
       </c>
       <c r="F54" t="s">
@@ -3845,25 +3847,25 @@
       <c r="Q54" s="2">
         <v>13</v>
       </c>
-      <c r="S54" t="s">
+      <c r="R54" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
         <v>44410</v>
       </c>
       <c r="B55" s="4">
-        <v>44570</v>
-      </c>
-      <c r="C55" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C55" s="17">
         <f t="shared" si="0"/>
-        <v>160</v>
+        <v>107</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
       </c>
-      <c r="E55" s="17">
+      <c r="E55" s="14">
         <v>1411</v>
       </c>
       <c r="F55" t="s">
@@ -3897,25 +3899,25 @@
       <c r="Q55" s="2">
         <v>8.8000000000000007</v>
       </c>
-      <c r="S55" t="s">
+      <c r="R55" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
         <v>44407</v>
       </c>
       <c r="B56" s="4">
-        <v>44571</v>
-      </c>
-      <c r="C56" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C56" s="17">
         <f t="shared" si="0"/>
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="D56" t="s">
         <v>10</v>
       </c>
-      <c r="E56" s="17">
+      <c r="E56" s="14">
         <v>1317</v>
       </c>
       <c r="F56" t="s">
@@ -3955,25 +3957,25 @@
       <c r="Q56" s="2">
         <v>26.7</v>
       </c>
-      <c r="S56" t="s">
+      <c r="R56" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
         <v>44407</v>
       </c>
       <c r="B57" s="4">
-        <v>44572</v>
-      </c>
-      <c r="C57" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C57" s="17">
         <f t="shared" si="0"/>
-        <v>165</v>
+        <v>110</v>
       </c>
       <c r="D57" t="s">
         <v>10</v>
       </c>
-      <c r="E57" s="17">
+      <c r="E57" s="14">
         <v>857</v>
       </c>
       <c r="F57" t="s">
@@ -4013,25 +4015,25 @@
       <c r="Q57" s="2">
         <v>14.3</v>
       </c>
-      <c r="S57" t="s">
+      <c r="R57" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
         <v>44407</v>
       </c>
       <c r="B58" s="4">
-        <v>44573</v>
-      </c>
-      <c r="C58" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C58" s="17">
         <f t="shared" si="0"/>
-        <v>166</v>
+        <v>110</v>
       </c>
       <c r="D58" t="s">
         <v>2</v>
       </c>
-      <c r="E58" s="17">
+      <c r="E58" s="14">
         <v>703</v>
       </c>
       <c r="F58" t="s">
@@ -4065,25 +4067,25 @@
       <c r="Q58" s="2">
         <v>24</v>
       </c>
-      <c r="S58" t="s">
+      <c r="R58" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
         <v>44407</v>
       </c>
       <c r="B59" s="4">
-        <v>44574</v>
-      </c>
-      <c r="C59" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C59" s="17">
         <f t="shared" si="0"/>
-        <v>167</v>
+        <v>110</v>
       </c>
       <c r="D59" t="s">
         <v>19</v>
       </c>
-      <c r="E59" s="17">
+      <c r="E59" s="14">
         <v>4066</v>
       </c>
       <c r="F59" t="s">
@@ -4119,25 +4121,25 @@
       <c r="Q59" s="2">
         <v>15</v>
       </c>
-      <c r="S59" t="s">
+      <c r="R59" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
         <v>44407</v>
       </c>
       <c r="B60" s="4">
-        <v>44575</v>
-      </c>
-      <c r="C60" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C60" s="17">
         <f t="shared" si="0"/>
-        <v>168</v>
+        <v>110</v>
       </c>
       <c r="D60" t="s">
         <v>19</v>
       </c>
-      <c r="E60" s="17">
+      <c r="E60" s="14">
         <v>4066</v>
       </c>
       <c r="F60" t="s">
@@ -4171,25 +4173,25 @@
       <c r="O60" s="2"/>
       <c r="P60" s="2"/>
       <c r="Q60" s="2"/>
-      <c r="S60" t="s">
+      <c r="R60" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
         <v>44403</v>
       </c>
       <c r="B61" s="4">
-        <v>44576</v>
-      </c>
-      <c r="C61" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C61" s="17">
         <f t="shared" si="0"/>
-        <v>173</v>
+        <v>114</v>
       </c>
       <c r="D61" t="s">
         <v>28</v>
       </c>
-      <c r="E61" s="17">
+      <c r="E61" s="14">
         <v>1844</v>
       </c>
       <c r="F61" t="s">
@@ -4223,25 +4225,25 @@
       <c r="Q61" s="2">
         <v>9</v>
       </c>
-      <c r="S61" t="s">
+      <c r="R61" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
         <v>44400</v>
       </c>
       <c r="B62" s="4">
-        <v>44577</v>
-      </c>
-      <c r="C62" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C62" s="17">
         <f t="shared" si="0"/>
-        <v>177</v>
+        <v>117</v>
       </c>
       <c r="D62" t="s">
         <v>2</v>
       </c>
-      <c r="E62" s="17">
+      <c r="E62" s="14">
         <v>700</v>
       </c>
       <c r="F62" t="s">
@@ -4275,25 +4277,25 @@
       <c r="Q62" s="2">
         <v>16</v>
       </c>
-      <c r="S62" t="s">
+      <c r="R62" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A63" s="4">
         <v>44392</v>
       </c>
       <c r="B63" s="4">
-        <v>44578</v>
-      </c>
-      <c r="C63" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C63" s="17">
         <f t="shared" si="0"/>
-        <v>186</v>
+        <v>125</v>
       </c>
       <c r="D63" t="s">
         <v>2</v>
       </c>
-      <c r="E63" s="17">
+      <c r="E63" s="14">
         <v>3200</v>
       </c>
       <c r="F63" t="s">
@@ -4329,25 +4331,25 @@
       <c r="Q63" s="2">
         <v>12</v>
       </c>
-      <c r="S63" t="s">
+      <c r="R63" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
         <v>44376</v>
       </c>
       <c r="B64" s="4">
-        <v>44579</v>
-      </c>
-      <c r="C64" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C64" s="17">
         <f t="shared" si="0"/>
-        <v>203</v>
+        <v>141</v>
       </c>
       <c r="D64" t="s">
         <v>9</v>
       </c>
-      <c r="E64" s="17">
+      <c r="E64" s="14">
         <v>1598</v>
       </c>
       <c r="F64" t="s">
@@ -4383,25 +4385,25 @@
       <c r="Q64" s="2">
         <v>13</v>
       </c>
-      <c r="S64" t="s">
+      <c r="R64" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
         <v>44375</v>
       </c>
       <c r="B65" s="4">
-        <v>44580</v>
-      </c>
-      <c r="C65" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C65" s="17">
         <f t="shared" si="0"/>
-        <v>205</v>
+        <v>142</v>
       </c>
       <c r="D65" t="s">
         <v>7</v>
       </c>
-      <c r="E65" s="17">
+      <c r="E65" s="14">
         <v>1396</v>
       </c>
       <c r="F65" t="s">
@@ -4437,25 +4439,25 @@
       <c r="Q65" s="2">
         <v>9.6</v>
       </c>
-      <c r="S65" t="s">
+      <c r="R65" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A66" s="4">
         <v>44371</v>
       </c>
       <c r="B66" s="4">
-        <v>44581</v>
-      </c>
-      <c r="C66" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C66" s="17">
         <f t="shared" si="0"/>
-        <v>210</v>
+        <v>146</v>
       </c>
       <c r="D66" t="s">
         <v>2</v>
       </c>
-      <c r="E66" s="17">
+      <c r="E66" s="14">
         <v>2388</v>
       </c>
       <c r="F66" t="s">
@@ -4491,25 +4493,25 @@
       <c r="Q66" s="2">
         <v>21</v>
       </c>
-      <c r="S66" t="s">
+      <c r="R66" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
         <v>44364</v>
       </c>
       <c r="B67" s="4">
-        <v>44582</v>
-      </c>
-      <c r="C67" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C67" s="17">
         <f t="shared" ref="C67:C130" si="2">B67-A67</f>
-        <v>218</v>
+        <v>153</v>
       </c>
       <c r="D67" t="s">
         <v>2</v>
       </c>
-      <c r="E67" s="17">
+      <c r="E67" s="14">
         <v>703</v>
       </c>
       <c r="F67" t="s">
@@ -4522,7 +4524,7 @@
         <v>0</v>
       </c>
       <c r="I67" s="11">
-        <f t="shared" ref="I67:I130" si="3">28-J67</f>
+        <f t="shared" ref="I67:I130" si="3">ABS(28-J67)</f>
         <v>23</v>
       </c>
       <c r="J67" s="2">
@@ -4545,25 +4547,25 @@
       <c r="Q67" s="2">
         <v>21</v>
       </c>
-      <c r="S67" t="s">
+      <c r="R67" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
         <v>44361</v>
       </c>
       <c r="B68" s="4">
-        <v>44583</v>
-      </c>
-      <c r="C68" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C68" s="17">
         <f t="shared" si="2"/>
-        <v>222</v>
+        <v>156</v>
       </c>
       <c r="D68" t="s">
         <v>23</v>
       </c>
-      <c r="E68" s="17">
+      <c r="E68" s="14">
         <v>1506</v>
       </c>
       <c r="F68" t="s">
@@ -4601,25 +4603,25 @@
       <c r="Q68" s="2">
         <v>39</v>
       </c>
-      <c r="S68" t="s">
+      <c r="R68" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A69" s="4">
         <v>44358</v>
       </c>
       <c r="B69" s="4">
-        <v>44584</v>
-      </c>
-      <c r="C69" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C69" s="17">
         <f t="shared" si="2"/>
-        <v>226</v>
+        <v>159</v>
       </c>
       <c r="D69" t="s">
         <v>10</v>
       </c>
-      <c r="E69" s="17">
+      <c r="E69" s="14">
         <v>1226</v>
       </c>
       <c r="F69" t="s">
@@ -4657,25 +4659,25 @@
       <c r="Q69" s="2">
         <v>18.600000000000001</v>
       </c>
-      <c r="S69" t="s">
+      <c r="R69" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
         <v>44358</v>
       </c>
       <c r="B70" s="4">
-        <v>44585</v>
-      </c>
-      <c r="C70" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C70" s="17">
         <f t="shared" si="2"/>
-        <v>227</v>
+        <v>159</v>
       </c>
       <c r="D70" t="s">
         <v>10</v>
       </c>
-      <c r="E70" s="17">
+      <c r="E70" s="14">
         <v>771</v>
       </c>
       <c r="F70" t="s">
@@ -4713,25 +4715,25 @@
       <c r="Q70" s="2">
         <v>12.7</v>
       </c>
-      <c r="S70" t="s">
+      <c r="R70" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A71" s="4">
         <v>44358</v>
       </c>
       <c r="B71" s="4">
-        <v>44586</v>
-      </c>
-      <c r="C71" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C71" s="17">
         <f t="shared" si="2"/>
-        <v>228</v>
+        <v>159</v>
       </c>
       <c r="D71" t="s">
         <v>2</v>
       </c>
-      <c r="E71" s="17">
+      <c r="E71" s="14">
         <v>703</v>
       </c>
       <c r="F71" t="s">
@@ -4767,25 +4769,25 @@
       <c r="Q71" s="2">
         <v>19</v>
       </c>
-      <c r="S71" t="s">
+      <c r="R71" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
         <v>44350</v>
       </c>
       <c r="B72" s="4">
-        <v>44587</v>
-      </c>
-      <c r="C72" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C72" s="17">
         <f t="shared" si="2"/>
-        <v>237</v>
+        <v>167</v>
       </c>
       <c r="D72" t="s">
         <v>2</v>
       </c>
-      <c r="E72" s="17">
+      <c r="E72" s="14">
         <v>702</v>
       </c>
       <c r="F72" t="s">
@@ -4821,25 +4823,25 @@
       <c r="Q72" s="2">
         <v>16</v>
       </c>
-      <c r="S72" t="s">
+      <c r="R72" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A73" s="4">
         <v>44348</v>
       </c>
       <c r="B73" s="4">
-        <v>44588</v>
-      </c>
-      <c r="C73" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C73" s="17">
         <f t="shared" si="2"/>
-        <v>240</v>
+        <v>169</v>
       </c>
       <c r="D73" t="s">
         <v>9</v>
       </c>
-      <c r="E73" s="17">
+      <c r="E73" s="14">
         <v>1532</v>
       </c>
       <c r="F73" t="s">
@@ -4875,25 +4877,25 @@
       <c r="Q73" s="2">
         <v>18</v>
       </c>
-      <c r="S73" t="s">
+      <c r="R73" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A74" s="4">
         <v>44347</v>
       </c>
       <c r="B74" s="4">
-        <v>44589</v>
-      </c>
-      <c r="C74" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C74" s="17">
         <f t="shared" si="2"/>
-        <v>242</v>
+        <v>170</v>
       </c>
       <c r="D74" t="s">
         <v>7</v>
       </c>
-      <c r="E74" s="17">
+      <c r="E74" s="14">
         <v>1365</v>
       </c>
       <c r="F74" t="s">
@@ -4929,25 +4931,25 @@
       <c r="Q74" s="2">
         <v>12.1</v>
       </c>
-      <c r="S74" t="s">
+      <c r="R74" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A75" s="4">
         <v>44344</v>
       </c>
       <c r="B75" s="4">
-        <v>44590</v>
-      </c>
-      <c r="C75" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C75" s="17">
         <f t="shared" si="2"/>
-        <v>246</v>
+        <v>173</v>
       </c>
       <c r="D75" t="s">
         <v>10</v>
       </c>
-      <c r="E75" s="17">
+      <c r="E75" s="14">
         <v>1522</v>
       </c>
       <c r="F75" t="s">
@@ -4983,25 +4985,25 @@
       <c r="Q75" s="2">
         <v>22.7</v>
       </c>
-      <c r="S75" t="s">
+      <c r="R75" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A76" s="4">
         <v>44344</v>
       </c>
       <c r="B76" s="4">
-        <v>44591</v>
-      </c>
-      <c r="C76" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C76" s="17">
         <f t="shared" si="2"/>
-        <v>247</v>
+        <v>173</v>
       </c>
       <c r="D76" t="s">
         <v>10</v>
       </c>
-      <c r="E76" s="17">
+      <c r="E76" s="14">
         <v>967</v>
       </c>
       <c r="F76" t="s">
@@ -5037,25 +5039,25 @@
       <c r="Q76" s="2">
         <v>15.5</v>
       </c>
-      <c r="S76" t="s">
+      <c r="R76" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A77" s="4">
         <v>44344</v>
       </c>
       <c r="B77" s="4">
-        <v>44592</v>
-      </c>
-      <c r="C77" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C77" s="17">
         <f t="shared" si="2"/>
-        <v>248</v>
+        <v>173</v>
       </c>
       <c r="D77" t="s">
         <v>19</v>
       </c>
-      <c r="E77" s="17">
+      <c r="E77" s="14">
         <v>5457</v>
       </c>
       <c r="F77" t="s">
@@ -5089,25 +5091,25 @@
       <c r="Q77" s="2">
         <v>40</v>
       </c>
-      <c r="S77" t="s">
+      <c r="R77" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A78" s="4">
         <v>44334</v>
       </c>
       <c r="B78" s="4">
-        <v>44593</v>
-      </c>
-      <c r="C78" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C78" s="17">
         <f t="shared" si="2"/>
-        <v>259</v>
+        <v>183</v>
       </c>
       <c r="D78" t="s">
         <v>10</v>
       </c>
-      <c r="E78" s="17">
+      <c r="E78" s="14">
         <v>1047</v>
       </c>
       <c r="F78" t="s">
@@ -5141,25 +5143,25 @@
       <c r="Q78" s="2">
         <v>24.5</v>
       </c>
-      <c r="S78" t="s">
+      <c r="R78" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
         <v>44334</v>
       </c>
       <c r="B79" s="4">
-        <v>44594</v>
-      </c>
-      <c r="C79" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C79" s="17">
         <f t="shared" si="2"/>
-        <v>260</v>
+        <v>183</v>
       </c>
       <c r="D79" t="s">
         <v>10</v>
       </c>
-      <c r="E79" s="17">
+      <c r="E79" s="14">
         <v>680</v>
       </c>
       <c r="F79" t="s">
@@ -5193,25 +5195,25 @@
       <c r="Q79" s="2">
         <v>17.3</v>
       </c>
-      <c r="S79" t="s">
+      <c r="R79" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A80" s="4">
         <v>44319</v>
       </c>
       <c r="B80" s="4">
-        <v>44595</v>
-      </c>
-      <c r="C80" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C80" s="17">
         <f t="shared" si="2"/>
-        <v>276</v>
+        <v>198</v>
       </c>
       <c r="D80" t="s">
         <v>9</v>
       </c>
-      <c r="E80" s="17">
+      <c r="E80" s="14">
         <v>1592</v>
       </c>
       <c r="F80" t="s">
@@ -5245,25 +5247,25 @@
       <c r="Q80" s="2">
         <v>18</v>
       </c>
-      <c r="S80" t="s">
+      <c r="R80" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A81" s="4">
         <v>44316</v>
       </c>
       <c r="B81" s="4">
-        <v>44596</v>
-      </c>
-      <c r="C81" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C81" s="17">
         <f t="shared" si="2"/>
-        <v>280</v>
+        <v>201</v>
       </c>
       <c r="D81" t="s">
         <v>10</v>
       </c>
-      <c r="E81" s="17">
+      <c r="E81" s="14">
         <v>1184</v>
       </c>
       <c r="F81" t="s">
@@ -5297,25 +5299,25 @@
       <c r="Q81" s="2">
         <v>23.2</v>
       </c>
-      <c r="S81" t="s">
+      <c r="R81" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A82" s="4">
         <v>44316</v>
       </c>
       <c r="B82" s="4">
-        <v>44597</v>
-      </c>
-      <c r="C82" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C82" s="17">
         <f t="shared" si="2"/>
-        <v>281</v>
+        <v>201</v>
       </c>
       <c r="D82" t="s">
         <v>10</v>
       </c>
-      <c r="E82" s="17">
+      <c r="E82" s="14">
         <v>667</v>
       </c>
       <c r="F82" t="s">
@@ -5349,25 +5351,25 @@
       <c r="Q82" s="2">
         <v>16.399999999999999</v>
       </c>
-      <c r="S82" t="s">
+      <c r="R82" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A83" s="4">
         <v>44312</v>
       </c>
       <c r="B83" s="4">
-        <v>44598</v>
-      </c>
-      <c r="C83" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C83" s="17">
         <f t="shared" si="2"/>
-        <v>286</v>
+        <v>205</v>
       </c>
       <c r="D83" t="s">
         <v>7</v>
       </c>
-      <c r="E83" s="17">
+      <c r="E83" s="14">
         <v>2014</v>
       </c>
       <c r="F83" t="s">
@@ -5403,25 +5405,25 @@
       <c r="Q83" s="2">
         <v>13.8</v>
       </c>
-      <c r="S83" t="s">
+      <c r="R83" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A84" s="4">
         <v>44302</v>
       </c>
       <c r="B84" s="4">
-        <v>44599</v>
-      </c>
-      <c r="C84" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C84" s="17">
         <f t="shared" si="2"/>
-        <v>297</v>
+        <v>215</v>
       </c>
       <c r="D84" t="s">
         <v>10</v>
       </c>
-      <c r="E84" s="17">
+      <c r="E84" s="14">
         <v>1054</v>
       </c>
       <c r="F84" t="s">
@@ -5457,25 +5459,25 @@
       <c r="Q84" s="2">
         <v>23.2</v>
       </c>
-      <c r="S84" t="s">
+      <c r="R84" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A85" s="4">
         <v>44302</v>
       </c>
       <c r="B85" s="4">
-        <v>44600</v>
-      </c>
-      <c r="C85" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C85" s="17">
         <f t="shared" si="2"/>
-        <v>298</v>
+        <v>215</v>
       </c>
       <c r="D85" t="s">
         <v>10</v>
       </c>
-      <c r="E85" s="17">
+      <c r="E85" s="14">
         <v>623</v>
       </c>
       <c r="F85" t="s">
@@ -5511,25 +5513,25 @@
       <c r="Q85" s="2">
         <v>13.9</v>
       </c>
-      <c r="S85" t="s">
+      <c r="R85" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A86" s="4">
         <v>44285</v>
       </c>
       <c r="B86" s="4">
-        <v>44601</v>
-      </c>
-      <c r="C86" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C86" s="17">
         <f t="shared" si="2"/>
-        <v>316</v>
+        <v>232</v>
       </c>
       <c r="D86" t="s">
         <v>9</v>
       </c>
-      <c r="E86" s="17">
+      <c r="E86" s="14">
         <v>1641</v>
       </c>
       <c r="F86" t="s">
@@ -5561,25 +5563,25 @@
       <c r="Q86" s="2">
         <v>17</v>
       </c>
-      <c r="S86" t="s">
+      <c r="R86" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A87" s="4">
         <v>44284</v>
       </c>
       <c r="B87" s="4">
-        <v>44602</v>
-      </c>
-      <c r="C87" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C87" s="17">
         <f t="shared" si="2"/>
-        <v>318</v>
+        <v>233</v>
       </c>
       <c r="D87" t="s">
         <v>10</v>
       </c>
-      <c r="E87" s="17">
+      <c r="E87" s="14">
         <v>1255</v>
       </c>
       <c r="F87" t="s">
@@ -5615,25 +5617,25 @@
       <c r="Q87" s="2">
         <v>23.3</v>
       </c>
-      <c r="S87" t="s">
+      <c r="R87" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A88" s="4">
         <v>44284</v>
       </c>
       <c r="B88" s="4">
-        <v>44603</v>
-      </c>
-      <c r="C88" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C88" s="17">
         <f t="shared" si="2"/>
-        <v>319</v>
+        <v>233</v>
       </c>
       <c r="D88" t="s">
         <v>10</v>
       </c>
-      <c r="E88" s="17">
+      <c r="E88" s="14">
         <v>693</v>
       </c>
       <c r="F88" t="s">
@@ -5669,25 +5671,25 @@
       <c r="Q88" s="2">
         <v>15</v>
       </c>
-      <c r="S88" t="s">
+      <c r="R88" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A89" s="4">
         <v>44267</v>
       </c>
       <c r="B89" s="4">
-        <v>44604</v>
-      </c>
-      <c r="C89" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C89" s="17">
         <f t="shared" si="2"/>
-        <v>337</v>
+        <v>250</v>
       </c>
       <c r="D89" t="s">
         <v>10</v>
       </c>
-      <c r="E89" s="17">
+      <c r="E89" s="14">
         <v>1235</v>
       </c>
       <c r="F89" t="s">
@@ -5723,25 +5725,25 @@
       <c r="Q89" s="2">
         <v>22.5</v>
       </c>
-      <c r="S89" t="s">
+      <c r="R89" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
         <v>44267</v>
       </c>
       <c r="B90" s="4">
-        <v>44605</v>
-      </c>
-      <c r="C90" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C90" s="17">
         <f t="shared" si="2"/>
-        <v>338</v>
+        <v>250</v>
       </c>
       <c r="D90" t="s">
         <v>10</v>
       </c>
-      <c r="E90" s="17">
+      <c r="E90" s="14">
         <v>747</v>
       </c>
       <c r="F90" t="s">
@@ -5777,25 +5779,25 @@
       <c r="Q90" s="2">
         <v>16.5</v>
       </c>
-      <c r="S90" t="s">
+      <c r="R90" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A91" s="4">
         <v>44260</v>
       </c>
       <c r="B91" s="4">
-        <v>44606</v>
-      </c>
-      <c r="C91" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C91" s="17">
         <f t="shared" si="2"/>
-        <v>346</v>
+        <v>257</v>
       </c>
       <c r="D91" t="s">
         <v>2</v>
       </c>
-      <c r="E91" s="17">
+      <c r="E91" s="14">
         <v>705</v>
       </c>
       <c r="F91" t="s">
@@ -5829,25 +5831,25 @@
       <c r="Q91" s="2">
         <v>66</v>
       </c>
-      <c r="S91" t="s">
+      <c r="R91" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A92" s="4">
         <v>44255</v>
       </c>
       <c r="B92" s="4">
-        <v>44607</v>
-      </c>
-      <c r="C92" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C92" s="17">
         <f t="shared" si="2"/>
-        <v>352</v>
+        <v>262</v>
       </c>
       <c r="D92" t="s">
         <v>7</v>
       </c>
-      <c r="E92" s="17">
+      <c r="E92" s="14">
         <v>1637</v>
       </c>
       <c r="F92" t="s">
@@ -5883,25 +5885,25 @@
       <c r="Q92" s="2">
         <v>21.7</v>
       </c>
-      <c r="S92" t="s">
+      <c r="R92" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A93" s="4">
         <v>44239</v>
       </c>
       <c r="B93" s="4">
-        <v>44608</v>
-      </c>
-      <c r="C93" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C93" s="17">
         <f t="shared" si="2"/>
-        <v>369</v>
+        <v>278</v>
       </c>
       <c r="D93" t="s">
         <v>10</v>
       </c>
-      <c r="E93" s="17">
+      <c r="E93" s="14">
         <v>1003</v>
       </c>
       <c r="F93" t="s">
@@ -5935,25 +5937,25 @@
       <c r="Q93" s="2">
         <v>25.3</v>
       </c>
-      <c r="S93" t="s">
+      <c r="R93" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A94" s="4">
         <v>44239</v>
       </c>
       <c r="B94" s="4">
-        <v>44609</v>
-      </c>
-      <c r="C94" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C94" s="17">
         <f t="shared" si="2"/>
-        <v>370</v>
+        <v>278</v>
       </c>
       <c r="D94" t="s">
         <v>10</v>
       </c>
-      <c r="E94" s="17">
+      <c r="E94" s="14">
         <v>581</v>
       </c>
       <c r="F94" t="s">
@@ -5989,25 +5991,25 @@
       <c r="Q94" s="2">
         <v>20.100000000000001</v>
       </c>
-      <c r="S94" t="s">
+      <c r="R94" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A95" s="4">
         <v>44239</v>
       </c>
       <c r="B95" s="4">
-        <v>44610</v>
-      </c>
-      <c r="C95" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C95" s="17">
         <f t="shared" si="2"/>
-        <v>371</v>
+        <v>278</v>
       </c>
       <c r="D95" t="s">
         <v>2</v>
       </c>
-      <c r="E95" s="17">
+      <c r="E95" s="14">
         <v>705</v>
       </c>
       <c r="F95" t="s">
@@ -6041,25 +6043,25 @@
       <c r="Q95" s="2">
         <v>65</v>
       </c>
-      <c r="S95" t="s">
+      <c r="R95" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A96" s="4">
         <v>44232</v>
       </c>
       <c r="B96" s="4">
-        <v>44611</v>
-      </c>
-      <c r="C96" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C96" s="17">
         <f t="shared" si="2"/>
-        <v>379</v>
+        <v>285</v>
       </c>
       <c r="D96" t="s">
         <v>2</v>
       </c>
-      <c r="E96" s="17">
+      <c r="E96" s="14">
         <v>704</v>
       </c>
       <c r="F96" t="s">
@@ -6093,25 +6095,25 @@
       <c r="Q96" s="2">
         <v>57</v>
       </c>
-      <c r="S96" t="s">
+      <c r="R96" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A97" s="4">
         <v>44228</v>
       </c>
       <c r="B97" s="4">
-        <v>44612</v>
-      </c>
-      <c r="C97" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C97" s="17">
         <f t="shared" si="2"/>
-        <v>384</v>
+        <v>289</v>
       </c>
       <c r="D97" t="s">
         <v>9</v>
       </c>
-      <c r="E97" s="17">
+      <c r="E97" s="14">
         <v>1000</v>
       </c>
       <c r="F97" t="s">
@@ -6143,25 +6145,25 @@
       <c r="Q97" s="2">
         <v>20</v>
       </c>
-      <c r="S97" t="s">
+      <c r="R97" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A98" s="4">
         <v>44228</v>
       </c>
       <c r="B98" s="4">
-        <v>44613</v>
-      </c>
-      <c r="C98" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C98" s="17">
         <f t="shared" si="2"/>
-        <v>385</v>
+        <v>289</v>
       </c>
       <c r="D98" t="s">
         <v>7</v>
       </c>
-      <c r="E98" s="17">
+      <c r="E98" s="14">
         <v>1613</v>
       </c>
       <c r="F98" t="s">
@@ -6197,25 +6199,25 @@
       <c r="Q98" s="2">
         <v>13.9</v>
       </c>
-      <c r="S98" t="s">
+      <c r="R98" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A99" s="4">
         <v>44225</v>
       </c>
       <c r="B99" s="4">
-        <v>44614</v>
-      </c>
-      <c r="C99" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C99" s="17">
         <f t="shared" si="2"/>
-        <v>389</v>
+        <v>292</v>
       </c>
       <c r="D99" t="s">
         <v>10</v>
       </c>
-      <c r="E99" s="17">
+      <c r="E99" s="14">
         <v>1041</v>
       </c>
       <c r="F99" t="s">
@@ -6247,25 +6249,25 @@
       <c r="Q99" s="2">
         <v>25.2</v>
       </c>
-      <c r="S99" t="s">
+      <c r="R99" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A100" s="4">
         <v>44225</v>
       </c>
       <c r="B100" s="4">
-        <v>44615</v>
-      </c>
-      <c r="C100" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C100" s="17">
         <f t="shared" si="2"/>
-        <v>390</v>
+        <v>292</v>
       </c>
       <c r="D100" t="s">
         <v>10</v>
       </c>
-      <c r="E100" s="17">
+      <c r="E100" s="14">
         <v>636</v>
       </c>
       <c r="F100" t="s">
@@ -6297,25 +6299,25 @@
       <c r="Q100" s="2">
         <v>16.600000000000001</v>
       </c>
-      <c r="S100" t="s">
+      <c r="R100" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
         <v>44225</v>
       </c>
       <c r="B101" s="4">
-        <v>44616</v>
-      </c>
-      <c r="C101" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C101" s="17">
         <f t="shared" si="2"/>
-        <v>391</v>
+        <v>292</v>
       </c>
       <c r="D101" t="s">
         <v>2</v>
       </c>
-      <c r="E101" s="17">
+      <c r="E101" s="14">
         <v>702</v>
       </c>
       <c r="F101" t="s">
@@ -6347,25 +6349,25 @@
       <c r="Q101" s="2">
         <v>59</v>
       </c>
-      <c r="S101" t="s">
+      <c r="R101" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A102" s="4">
         <v>44218</v>
       </c>
       <c r="B102" s="4">
-        <v>44617</v>
-      </c>
-      <c r="C102" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C102" s="17">
         <f t="shared" si="2"/>
-        <v>399</v>
+        <v>299</v>
       </c>
       <c r="D102" t="s">
         <v>2</v>
       </c>
-      <c r="E102" s="17">
+      <c r="E102" s="14">
         <v>710</v>
       </c>
       <c r="F102" t="s">
@@ -6397,25 +6399,25 @@
       <c r="Q102" s="2">
         <v>57</v>
       </c>
-      <c r="S102" t="s">
+      <c r="R102" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A103" s="4">
         <v>44211</v>
       </c>
       <c r="B103" s="4">
-        <v>44618</v>
-      </c>
-      <c r="C103" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C103" s="17">
         <f t="shared" si="2"/>
-        <v>407</v>
+        <v>306</v>
       </c>
       <c r="D103" t="s">
         <v>10</v>
       </c>
-      <c r="E103" s="17">
+      <c r="E103" s="14">
         <v>1003</v>
       </c>
       <c r="F103" t="s">
@@ -6449,25 +6451,25 @@
       <c r="Q103" s="2">
         <v>22.1</v>
       </c>
-      <c r="S103" t="s">
+      <c r="R103" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A104" s="4">
         <v>44211</v>
       </c>
       <c r="B104" s="4">
-        <v>44619</v>
-      </c>
-      <c r="C104" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C104" s="17">
         <f t="shared" si="2"/>
-        <v>408</v>
+        <v>306</v>
       </c>
       <c r="D104" t="s">
         <v>10</v>
       </c>
-      <c r="E104" s="17">
+      <c r="E104" s="14">
         <v>601</v>
       </c>
       <c r="F104" t="s">
@@ -6501,25 +6503,25 @@
       <c r="Q104" s="2">
         <v>11</v>
       </c>
-      <c r="S104" t="s">
+      <c r="R104" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A105" s="4">
         <v>44211</v>
       </c>
       <c r="B105" s="4">
-        <v>44620</v>
-      </c>
-      <c r="C105" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C105" s="17">
         <f t="shared" si="2"/>
-        <v>409</v>
+        <v>306</v>
       </c>
       <c r="D105" t="s">
         <v>2</v>
       </c>
-      <c r="E105" s="17">
+      <c r="E105" s="14">
         <v>704</v>
       </c>
       <c r="F105" t="s">
@@ -6549,25 +6551,25 @@
       <c r="Q105" s="2">
         <v>60</v>
       </c>
-      <c r="S105" t="s">
+      <c r="R105" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A106" s="4">
         <v>44201</v>
       </c>
       <c r="B106" s="4">
-        <v>44621</v>
-      </c>
-      <c r="C106" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C106" s="17">
         <f t="shared" si="2"/>
-        <v>420</v>
+        <v>316</v>
       </c>
       <c r="D106" t="s">
         <v>9</v>
       </c>
-      <c r="E106" s="17">
+      <c r="E106" s="14">
         <v>1550</v>
       </c>
       <c r="F106" t="s">
@@ -6601,25 +6603,25 @@
       <c r="Q106" s="2">
         <v>15</v>
       </c>
-      <c r="S106" t="s">
+      <c r="R106" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A107" s="4">
         <v>44200</v>
       </c>
       <c r="B107" s="4">
-        <v>44622</v>
-      </c>
-      <c r="C107" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C107" s="17">
         <f t="shared" si="2"/>
-        <v>422</v>
+        <v>317</v>
       </c>
       <c r="D107" t="s">
         <v>7</v>
       </c>
-      <c r="E107" s="17">
+      <c r="E107" s="14">
         <v>1568</v>
       </c>
       <c r="F107" t="s">
@@ -6653,25 +6655,25 @@
       <c r="Q107" s="2">
         <v>14</v>
       </c>
-      <c r="S107" t="s">
+      <c r="R107" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A108" s="4">
         <v>44196</v>
       </c>
       <c r="B108" s="4">
-        <v>44623</v>
-      </c>
-      <c r="C108" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C108" s="17">
         <f t="shared" si="2"/>
-        <v>427</v>
+        <v>321</v>
       </c>
       <c r="D108" t="s">
         <v>2</v>
       </c>
-      <c r="E108" s="17">
+      <c r="E108" s="14">
         <v>704</v>
       </c>
       <c r="F108" t="s">
@@ -6703,25 +6705,25 @@
       <c r="Q108" s="2">
         <v>60</v>
       </c>
-      <c r="S108" t="s">
+      <c r="R108" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A109" s="4">
         <v>44193</v>
       </c>
       <c r="B109" s="4">
-        <v>44624</v>
-      </c>
-      <c r="C109" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C109" s="17">
         <f t="shared" si="2"/>
-        <v>431</v>
+        <v>324</v>
       </c>
       <c r="D109" t="s">
         <v>10</v>
       </c>
-      <c r="E109" s="17">
+      <c r="E109" s="14">
         <v>1004</v>
       </c>
       <c r="F109" t="s">
@@ -6753,25 +6755,25 @@
       <c r="Q109" s="2">
         <v>24.4</v>
       </c>
-      <c r="S109" t="s">
+      <c r="R109" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A110" s="4">
         <v>44193</v>
       </c>
       <c r="B110" s="4">
-        <v>44625</v>
-      </c>
-      <c r="C110" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C110" s="17">
         <f t="shared" si="2"/>
-        <v>432</v>
+        <v>324</v>
       </c>
       <c r="D110" t="s">
         <v>10</v>
       </c>
-      <c r="E110" s="17">
+      <c r="E110" s="14">
         <v>606</v>
       </c>
       <c r="F110" t="s">
@@ -6803,25 +6805,25 @@
       <c r="Q110" s="2">
         <v>19.3</v>
       </c>
-      <c r="S110" t="s">
+      <c r="R110" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A111" s="4">
         <v>44175</v>
       </c>
       <c r="B111" s="4">
-        <v>44626</v>
-      </c>
-      <c r="C111" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C111" s="17">
         <f t="shared" si="2"/>
-        <v>451</v>
+        <v>342</v>
       </c>
       <c r="D111" t="s">
         <v>2</v>
       </c>
-      <c r="E111" s="17">
+      <c r="E111" s="14">
         <v>703</v>
       </c>
       <c r="F111" t="s">
@@ -6853,25 +6855,25 @@
       <c r="Q111" s="2">
         <v>54</v>
       </c>
-      <c r="S111" t="s">
+      <c r="R111" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
         <v>44174</v>
       </c>
       <c r="B112" s="4">
-        <v>44627</v>
-      </c>
-      <c r="C112" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C112" s="17">
         <f t="shared" si="2"/>
-        <v>453</v>
+        <v>343</v>
       </c>
       <c r="D112" t="s">
         <v>9</v>
       </c>
-      <c r="E112" s="17">
+      <c r="E112" s="14">
         <v>957</v>
       </c>
       <c r="F112" t="s">
@@ -6903,25 +6905,25 @@
       <c r="Q112" s="2">
         <v>17</v>
       </c>
-      <c r="S112" t="s">
+      <c r="R112" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A113" s="4">
         <v>44165</v>
       </c>
       <c r="B113" s="4">
-        <v>44628</v>
-      </c>
-      <c r="C113" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C113" s="17">
         <f t="shared" si="2"/>
-        <v>463</v>
+        <v>352</v>
       </c>
       <c r="D113" t="s">
         <v>7</v>
       </c>
-      <c r="E113" s="17">
+      <c r="E113" s="14">
         <v>1702</v>
       </c>
       <c r="F113" t="s">
@@ -6955,25 +6957,25 @@
       <c r="Q113" s="2">
         <v>15.5</v>
       </c>
-      <c r="S113" t="s">
+      <c r="R113" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A114" s="4">
         <v>44163</v>
       </c>
       <c r="B114" s="4">
-        <v>44629</v>
-      </c>
-      <c r="C114" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C114" s="17">
         <f t="shared" si="2"/>
-        <v>466</v>
+        <v>354</v>
       </c>
       <c r="D114" t="s">
         <v>10</v>
       </c>
-      <c r="E114" s="17">
+      <c r="E114" s="14">
         <v>1177</v>
       </c>
       <c r="F114" t="s">
@@ -7003,25 +7005,25 @@
       <c r="Q114" s="2">
         <v>26.4</v>
       </c>
-      <c r="S114" t="s">
+      <c r="R114" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A115" s="4">
         <v>44163</v>
       </c>
       <c r="B115" s="4">
-        <v>44630</v>
-      </c>
-      <c r="C115" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C115" s="17">
         <f t="shared" si="2"/>
-        <v>467</v>
+        <v>354</v>
       </c>
       <c r="D115" t="s">
         <v>10</v>
       </c>
-      <c r="E115" s="17">
+      <c r="E115" s="14">
         <v>657</v>
       </c>
       <c r="F115" t="s">
@@ -7051,25 +7053,25 @@
       <c r="Q115" s="2">
         <v>23.7</v>
       </c>
-      <c r="S115" t="s">
+      <c r="R115" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A116" s="4">
         <v>44149</v>
       </c>
       <c r="B116" s="4">
-        <v>44631</v>
-      </c>
-      <c r="C116" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C116" s="17">
         <f t="shared" si="2"/>
-        <v>482</v>
+        <v>368</v>
       </c>
       <c r="D116" t="s">
         <v>10</v>
       </c>
-      <c r="E116" s="17">
+      <c r="E116" s="14">
         <v>1035</v>
       </c>
       <c r="F116" t="s">
@@ -7099,25 +7101,25 @@
       <c r="Q116" s="2">
         <v>23.9</v>
       </c>
-      <c r="S116" t="s">
+      <c r="R116" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A117" s="4">
         <v>44149</v>
       </c>
       <c r="B117" s="4">
-        <v>44632</v>
-      </c>
-      <c r="C117" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C117" s="17">
         <f t="shared" si="2"/>
-        <v>483</v>
+        <v>368</v>
       </c>
       <c r="D117" t="s">
         <v>10</v>
       </c>
-      <c r="E117" s="17">
+      <c r="E117" s="14">
         <v>657</v>
       </c>
       <c r="F117" t="s">
@@ -7147,25 +7149,25 @@
       <c r="Q117" s="2">
         <v>16.600000000000001</v>
       </c>
-      <c r="S117" t="s">
+      <c r="R117" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A118" s="4">
         <v>44148</v>
       </c>
       <c r="B118" s="4">
-        <v>44633</v>
-      </c>
-      <c r="C118" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C118" s="17">
         <f t="shared" si="2"/>
-        <v>485</v>
+        <v>369</v>
       </c>
       <c r="D118" t="s">
         <v>2</v>
       </c>
-      <c r="E118" s="17">
+      <c r="E118" s="14">
         <v>706</v>
       </c>
       <c r="F118" t="s">
@@ -7197,25 +7199,25 @@
       <c r="Q118" s="2">
         <v>43</v>
       </c>
-      <c r="S118" t="s">
+      <c r="R118" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A119" s="4">
         <v>44141</v>
       </c>
       <c r="B119" s="4">
-        <v>44634</v>
-      </c>
-      <c r="C119" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C119" s="17">
         <f t="shared" si="2"/>
-        <v>493</v>
+        <v>376</v>
       </c>
       <c r="D119" t="s">
         <v>2</v>
       </c>
-      <c r="E119" s="17">
+      <c r="E119" s="14">
         <v>705</v>
       </c>
       <c r="F119" t="s">
@@ -7247,25 +7249,25 @@
       <c r="Q119" s="2">
         <v>63</v>
       </c>
-      <c r="S119" t="s">
+      <c r="R119" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A120" s="4">
         <v>44138</v>
       </c>
       <c r="B120" s="4">
-        <v>44635</v>
-      </c>
-      <c r="C120" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C120" s="17">
         <f t="shared" si="2"/>
-        <v>497</v>
+        <v>379</v>
       </c>
       <c r="D120" t="s">
         <v>9</v>
       </c>
-      <c r="E120" s="17">
+      <c r="E120" s="14">
         <v>1376</v>
       </c>
       <c r="F120" t="s">
@@ -7295,25 +7297,25 @@
       <c r="Q120" s="2">
         <v>14</v>
       </c>
-      <c r="S120" t="s">
+      <c r="R120" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A121" s="4">
         <v>44137</v>
       </c>
       <c r="B121" s="4">
-        <v>44636</v>
-      </c>
-      <c r="C121" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C121" s="17">
         <f t="shared" si="2"/>
-        <v>499</v>
+        <v>380</v>
       </c>
       <c r="D121" t="s">
         <v>7</v>
       </c>
-      <c r="E121" s="17">
+      <c r="E121" s="14">
         <v>2004</v>
       </c>
       <c r="F121" t="s">
@@ -7347,25 +7349,25 @@
       <c r="Q121" s="2">
         <v>11.1</v>
       </c>
-      <c r="S121" t="s">
+      <c r="R121" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A122" s="4">
         <v>44135</v>
       </c>
       <c r="B122" s="4">
-        <v>44637</v>
-      </c>
-      <c r="C122" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C122" s="17">
         <f t="shared" si="2"/>
-        <v>502</v>
+        <v>382</v>
       </c>
       <c r="D122" t="s">
         <v>10</v>
       </c>
-      <c r="E122" s="17">
+      <c r="E122" s="14">
         <v>1016</v>
       </c>
       <c r="F122" t="s">
@@ -7397,25 +7399,25 @@
       <c r="Q122" s="2">
         <v>26.9</v>
       </c>
-      <c r="S122" t="s">
+      <c r="R122" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
         <v>44135</v>
       </c>
       <c r="B123" s="4">
-        <v>44638</v>
-      </c>
-      <c r="C123" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C123" s="17">
         <f t="shared" si="2"/>
-        <v>503</v>
+        <v>382</v>
       </c>
       <c r="D123" t="s">
         <v>10</v>
       </c>
-      <c r="E123" s="17">
+      <c r="E123" s="14">
         <v>673</v>
       </c>
       <c r="F123" t="s">
@@ -7447,25 +7449,25 @@
       <c r="Q123" s="2">
         <v>13.9</v>
       </c>
-      <c r="S123" t="s">
+      <c r="R123" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A124" s="4">
         <v>44134</v>
       </c>
       <c r="B124" s="4">
-        <v>44639</v>
-      </c>
-      <c r="C124" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C124" s="17">
         <f t="shared" si="2"/>
-        <v>505</v>
+        <v>383</v>
       </c>
       <c r="D124" t="s">
         <v>2</v>
       </c>
-      <c r="E124" s="17">
+      <c r="E124" s="14">
         <v>707</v>
       </c>
       <c r="F124" t="s">
@@ -7495,25 +7497,25 @@
       <c r="Q124" s="2">
         <v>60</v>
       </c>
-      <c r="S124" t="s">
+      <c r="R124" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A125" s="4">
         <v>44121</v>
       </c>
       <c r="B125" s="4">
-        <v>44640</v>
-      </c>
-      <c r="C125" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C125" s="17">
         <f t="shared" si="2"/>
-        <v>519</v>
+        <v>396</v>
       </c>
       <c r="D125" t="s">
         <v>10</v>
       </c>
-      <c r="E125" s="17">
+      <c r="E125" s="14">
         <v>1458</v>
       </c>
       <c r="F125" t="s">
@@ -7543,25 +7545,25 @@
       <c r="Q125" s="2">
         <v>14.2</v>
       </c>
-      <c r="S125" t="s">
+      <c r="R125" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A126" s="4">
         <v>44112</v>
       </c>
       <c r="B126" s="4">
-        <v>44641</v>
-      </c>
-      <c r="C126" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C126" s="17">
         <f t="shared" si="2"/>
-        <v>529</v>
+        <v>405</v>
       </c>
       <c r="D126" t="s">
         <v>2</v>
       </c>
-      <c r="E126" s="17">
+      <c r="E126" s="14">
         <v>703</v>
       </c>
       <c r="F126" t="s">
@@ -7591,25 +7593,25 @@
       <c r="Q126" s="2">
         <v>65</v>
       </c>
-      <c r="S126" t="s">
+      <c r="R126" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A127" s="4">
         <v>44109</v>
       </c>
       <c r="B127" s="4">
-        <v>44642</v>
-      </c>
-      <c r="C127" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C127" s="17">
         <f t="shared" si="2"/>
-        <v>533</v>
+        <v>408</v>
       </c>
       <c r="D127" t="s">
         <v>7</v>
       </c>
-      <c r="E127" s="17">
+      <c r="E127" s="14">
         <v>2145</v>
       </c>
       <c r="F127" t="s">
@@ -7643,25 +7645,25 @@
       <c r="Q127" s="2">
         <v>13.3</v>
       </c>
-      <c r="S127" t="s">
+      <c r="R127" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A128" s="4">
         <v>44106</v>
       </c>
       <c r="B128" s="4">
-        <v>44643</v>
-      </c>
-      <c r="C128" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C128" s="17">
         <f t="shared" si="2"/>
-        <v>537</v>
+        <v>411</v>
       </c>
       <c r="D128" t="s">
         <v>2</v>
       </c>
-      <c r="E128" s="17">
+      <c r="E128" s="14">
         <v>705</v>
       </c>
       <c r="F128" t="s">
@@ -7693,25 +7695,25 @@
       <c r="Q128" s="2">
         <v>58</v>
       </c>
-      <c r="S128" t="s">
+      <c r="R128" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="129" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A129" s="4">
         <v>44104</v>
       </c>
       <c r="B129" s="4">
-        <v>44644</v>
-      </c>
-      <c r="C129" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C129" s="17">
         <f t="shared" si="2"/>
-        <v>540</v>
+        <v>413</v>
       </c>
       <c r="D129" t="s">
         <v>9</v>
       </c>
-      <c r="E129" s="17">
+      <c r="E129" s="14">
         <v>1503</v>
       </c>
       <c r="F129" t="s">
@@ -7741,25 +7743,25 @@
       <c r="Q129" s="2">
         <v>15</v>
       </c>
-      <c r="S129" t="s">
+      <c r="R129" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A130" s="4">
         <v>44102</v>
       </c>
       <c r="B130" s="4">
-        <v>44645</v>
-      </c>
-      <c r="C130" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C130" s="17">
         <f t="shared" si="2"/>
-        <v>543</v>
+        <v>415</v>
       </c>
       <c r="D130" t="s">
         <v>10</v>
       </c>
-      <c r="E130" s="17">
+      <c r="E130" s="14">
         <v>1417</v>
       </c>
       <c r="F130" t="s">
@@ -7791,25 +7793,25 @@
       <c r="Q130" s="2">
         <v>20</v>
       </c>
-      <c r="S130" t="s">
+      <c r="R130" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A131" s="4">
         <v>44099</v>
       </c>
       <c r="B131" s="4">
-        <v>44646</v>
-      </c>
-      <c r="C131" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C131" s="17">
         <f t="shared" ref="C131:C194" si="4">B131-A131</f>
-        <v>547</v>
+        <v>418</v>
       </c>
       <c r="D131" t="s">
         <v>2</v>
       </c>
-      <c r="E131" s="17">
+      <c r="E131" s="14">
         <v>702</v>
       </c>
       <c r="F131" t="s">
@@ -7822,7 +7824,7 @@
         <v>0</v>
       </c>
       <c r="I131" s="11">
-        <f t="shared" ref="I131:I194" si="5">28-J131</f>
+        <f t="shared" ref="I131:I194" si="5">ABS(28-J131)</f>
         <v>26</v>
       </c>
       <c r="J131" s="2">
@@ -7841,25 +7843,25 @@
       <c r="Q131" s="2">
         <v>60</v>
       </c>
-      <c r="S131" t="s">
+      <c r="R131" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="132" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A132" s="4">
         <v>44091</v>
       </c>
       <c r="B132" s="4">
-        <v>44647</v>
-      </c>
-      <c r="C132" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C132" s="17">
         <f t="shared" si="4"/>
-        <v>556</v>
+        <v>426</v>
       </c>
       <c r="D132" t="s">
         <v>2</v>
       </c>
-      <c r="E132" s="17">
+      <c r="E132" s="14">
         <v>704</v>
       </c>
       <c r="F132" t="s">
@@ -7891,25 +7893,25 @@
       <c r="Q132" s="2">
         <v>58</v>
       </c>
-      <c r="S132" t="s">
+      <c r="R132" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="133" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A133" s="4">
         <v>44091</v>
       </c>
       <c r="B133" s="4">
-        <v>44648</v>
-      </c>
-      <c r="C133" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C133" s="17">
         <f t="shared" si="4"/>
-        <v>557</v>
+        <v>426</v>
       </c>
       <c r="D133" t="s">
         <v>15</v>
       </c>
-      <c r="E133" s="17">
+      <c r="E133" s="14">
         <v>1000</v>
       </c>
       <c r="F133" t="s">
@@ -7939,25 +7941,25 @@
       <c r="Q133" s="2">
         <v>29</v>
       </c>
-      <c r="S133" t="s">
+      <c r="R133" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="134" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
         <v>44086</v>
       </c>
       <c r="B134" s="4">
-        <v>44649</v>
-      </c>
-      <c r="C134" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C134" s="17">
         <f t="shared" si="4"/>
-        <v>563</v>
+        <v>431</v>
       </c>
       <c r="D134" t="s">
         <v>10</v>
       </c>
-      <c r="E134" s="17">
+      <c r="E134" s="14">
         <v>1415</v>
       </c>
       <c r="F134" t="s">
@@ -7987,25 +7989,25 @@
       <c r="Q134" s="2">
         <v>21.2</v>
       </c>
-      <c r="S134" t="s">
+      <c r="R134" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A135" s="4">
         <v>44084</v>
       </c>
       <c r="B135" s="4">
-        <v>44650</v>
-      </c>
-      <c r="C135" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C135" s="17">
         <f t="shared" si="4"/>
-        <v>566</v>
+        <v>433</v>
       </c>
       <c r="D135" t="s">
         <v>2</v>
       </c>
-      <c r="E135" s="17">
+      <c r="E135" s="14">
         <v>705</v>
       </c>
       <c r="F135" t="s">
@@ -8037,25 +8039,25 @@
       <c r="Q135" s="2">
         <v>59</v>
       </c>
-      <c r="S135" t="s">
+      <c r="R135" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="136" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A136" s="4">
         <v>44074</v>
       </c>
       <c r="B136" s="4">
-        <v>44651</v>
-      </c>
-      <c r="C136" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C136" s="17">
         <f t="shared" si="4"/>
-        <v>577</v>
+        <v>443</v>
       </c>
       <c r="D136" t="s">
         <v>9</v>
       </c>
-      <c r="E136" s="17">
+      <c r="E136" s="14">
         <v>986</v>
       </c>
       <c r="F136" t="s">
@@ -8089,25 +8091,25 @@
       <c r="Q136" s="2">
         <v>16.3</v>
       </c>
-      <c r="S136" t="s">
+      <c r="R136" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A137" s="4">
         <v>44072</v>
       </c>
       <c r="B137" s="4">
-        <v>44652</v>
-      </c>
-      <c r="C137" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C137" s="17">
         <f t="shared" si="4"/>
-        <v>580</v>
+        <v>445</v>
       </c>
       <c r="D137" t="s">
         <v>10</v>
       </c>
-      <c r="E137" s="17">
+      <c r="E137" s="14">
         <v>1544</v>
       </c>
       <c r="F137" t="s">
@@ -8139,25 +8141,25 @@
       <c r="Q137" s="2">
         <v>22.6</v>
       </c>
-      <c r="S137" t="s">
+      <c r="R137" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A138" s="4">
         <v>44067</v>
       </c>
       <c r="B138" s="4">
-        <v>44653</v>
-      </c>
-      <c r="C138" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C138" s="17">
         <f t="shared" si="4"/>
-        <v>586</v>
+        <v>450</v>
       </c>
       <c r="D138" t="s">
         <v>7</v>
       </c>
-      <c r="E138" s="17">
+      <c r="E138" s="14">
         <v>1940</v>
       </c>
       <c r="F138" t="s">
@@ -8191,25 +8193,25 @@
       <c r="Q138" s="2">
         <v>12.9</v>
       </c>
-      <c r="S138" t="s">
+      <c r="R138" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A139" s="4">
         <v>44058</v>
       </c>
       <c r="B139" s="4">
-        <v>44654</v>
-      </c>
-      <c r="C139" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C139" s="17">
         <f t="shared" si="4"/>
-        <v>596</v>
+        <v>459</v>
       </c>
       <c r="D139" t="s">
         <v>10</v>
       </c>
-      <c r="E139" s="17">
+      <c r="E139" s="14">
         <v>1434</v>
       </c>
       <c r="F139" t="s">
@@ -8241,25 +8243,25 @@
       <c r="Q139" s="2">
         <v>27.2</v>
       </c>
-      <c r="S139" t="s">
+      <c r="R139" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A140" s="4">
         <v>44056</v>
       </c>
       <c r="B140" s="4">
-        <v>44655</v>
-      </c>
-      <c r="C140" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C140" s="17">
         <f t="shared" si="4"/>
-        <v>599</v>
+        <v>461</v>
       </c>
       <c r="D140" t="s">
         <v>2</v>
       </c>
-      <c r="E140" s="17">
+      <c r="E140" s="14">
         <v>703</v>
       </c>
       <c r="F140" t="s">
@@ -8292,21 +8294,21 @@
         <v>56</v>
       </c>
     </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A141" s="4">
         <v>44044</v>
       </c>
       <c r="B141" s="4">
-        <v>44656</v>
-      </c>
-      <c r="C141" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C141" s="17">
         <f t="shared" si="4"/>
-        <v>612</v>
+        <v>473</v>
       </c>
       <c r="D141" t="s">
         <v>10</v>
       </c>
-      <c r="E141" s="17">
+      <c r="E141" s="14">
         <v>1430</v>
       </c>
       <c r="F141" t="s">
@@ -8340,25 +8342,25 @@
       <c r="Q141" s="2">
         <v>27.2</v>
       </c>
-      <c r="S141" t="s">
+      <c r="R141" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="142" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A142" s="4">
         <v>44043</v>
       </c>
       <c r="B142" s="4">
-        <v>44657</v>
-      </c>
-      <c r="C142" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C142" s="17">
         <f t="shared" si="4"/>
-        <v>614</v>
+        <v>474</v>
       </c>
       <c r="D142" t="s">
         <v>9</v>
       </c>
-      <c r="E142" s="17">
+      <c r="E142" s="14">
         <v>800</v>
       </c>
       <c r="F142" t="s">
@@ -8392,25 +8394,25 @@
       <c r="Q142" s="2">
         <v>23</v>
       </c>
-      <c r="S142" t="s">
+      <c r="R142" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="143" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A143" s="4">
         <v>44038</v>
       </c>
       <c r="B143" s="4">
-        <v>44658</v>
-      </c>
-      <c r="C143" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C143" s="17">
         <f t="shared" si="4"/>
-        <v>620</v>
+        <v>479</v>
       </c>
       <c r="D143" t="s">
         <v>7</v>
       </c>
-      <c r="E143" s="17">
+      <c r="E143" s="14">
         <v>2034</v>
       </c>
       <c r="F143" t="s">
@@ -8444,25 +8446,25 @@
       <c r="Q143" s="2">
         <v>20</v>
       </c>
-      <c r="S143" t="s">
+      <c r="R143" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="144" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A144" s="4">
         <v>44023</v>
       </c>
       <c r="B144" s="4">
-        <v>44659</v>
-      </c>
-      <c r="C144" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C144" s="17">
         <f t="shared" si="4"/>
-        <v>636</v>
+        <v>494</v>
       </c>
       <c r="D144" t="s">
         <v>10</v>
       </c>
-      <c r="E144" s="17">
+      <c r="E144" s="14">
         <v>1340</v>
       </c>
       <c r="F144" t="s">
@@ -8496,25 +8498,25 @@
       <c r="Q144" s="2">
         <v>23.7</v>
       </c>
-      <c r="S144" t="s">
+      <c r="R144" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="145" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
         <v>44022</v>
       </c>
       <c r="B145" s="4">
-        <v>44660</v>
-      </c>
-      <c r="C145" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C145" s="17">
         <f t="shared" si="4"/>
-        <v>638</v>
+        <v>495</v>
       </c>
       <c r="D145" t="s">
         <v>2</v>
       </c>
-      <c r="E145" s="17">
+      <c r="E145" s="14">
         <v>704</v>
       </c>
       <c r="F145" t="s">
@@ -8547,21 +8549,21 @@
         <v>61</v>
       </c>
     </row>
-    <row r="146" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A146" s="4">
         <v>44012</v>
       </c>
       <c r="B146" s="4">
-        <v>44661</v>
-      </c>
-      <c r="C146" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C146" s="17">
         <f t="shared" si="4"/>
-        <v>649</v>
+        <v>505</v>
       </c>
       <c r="D146" t="s">
         <v>9</v>
       </c>
-      <c r="E146" s="17">
+      <c r="E146" s="14">
         <v>800</v>
       </c>
       <c r="F146" t="s">
@@ -8595,25 +8597,25 @@
       <c r="Q146" s="2">
         <v>16</v>
       </c>
-      <c r="S146" t="s">
+      <c r="R146" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="147" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A147" s="4">
         <v>44010</v>
       </c>
       <c r="B147" s="4">
-        <v>44662</v>
-      </c>
-      <c r="C147" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C147" s="17">
         <f t="shared" si="4"/>
-        <v>652</v>
+        <v>507</v>
       </c>
       <c r="D147" t="s">
         <v>10</v>
       </c>
-      <c r="E147" s="17">
+      <c r="E147" s="14">
         <v>1260</v>
       </c>
       <c r="F147" t="s">
@@ -8647,25 +8649,25 @@
       <c r="Q147" s="2">
         <v>24.7</v>
       </c>
-      <c r="S147" t="s">
+      <c r="R147" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="148" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A148" s="4">
         <v>44003</v>
       </c>
       <c r="B148" s="4">
-        <v>44663</v>
-      </c>
-      <c r="C148" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C148" s="17">
         <f t="shared" si="4"/>
-        <v>660</v>
+        <v>514</v>
       </c>
       <c r="D148" t="s">
         <v>7</v>
       </c>
-      <c r="E148" s="17">
+      <c r="E148" s="14">
         <v>1961</v>
       </c>
       <c r="F148" t="s">
@@ -8697,25 +8699,25 @@
       <c r="Q148" s="2">
         <v>20</v>
       </c>
-      <c r="S148" t="s">
+      <c r="R148" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="149" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A149" s="4">
         <v>43995</v>
       </c>
       <c r="B149" s="4">
-        <v>44664</v>
-      </c>
-      <c r="C149" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C149" s="17">
         <f t="shared" si="4"/>
-        <v>669</v>
+        <v>522</v>
       </c>
       <c r="D149" t="s">
         <v>10</v>
       </c>
-      <c r="E149" s="17">
+      <c r="E149" s="14">
         <v>1730</v>
       </c>
       <c r="F149" t="s">
@@ -8749,25 +8751,25 @@
       <c r="Q149" s="2">
         <v>30.2</v>
       </c>
-      <c r="S149" t="s">
+      <c r="R149" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="150" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A150" s="4">
         <v>43994</v>
       </c>
       <c r="B150" s="4">
-        <v>44665</v>
-      </c>
-      <c r="C150" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C150" s="17">
         <f t="shared" si="4"/>
-        <v>671</v>
+        <v>523</v>
       </c>
       <c r="D150" t="s">
         <v>2</v>
       </c>
-      <c r="E150" s="17">
+      <c r="E150" s="14">
         <v>705</v>
       </c>
       <c r="F150" t="s">
@@ -8798,21 +8800,21 @@
         <v>67</v>
       </c>
     </row>
-    <row r="151" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A151" s="4">
         <v>43982</v>
       </c>
       <c r="B151" s="4">
-        <v>44666</v>
-      </c>
-      <c r="C151" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C151" s="17">
         <f t="shared" si="4"/>
-        <v>684</v>
+        <v>535</v>
       </c>
       <c r="D151" t="s">
         <v>9</v>
       </c>
-      <c r="E151" s="17">
+      <c r="E151" s="14">
         <v>800</v>
       </c>
       <c r="F151" t="s">
@@ -8842,25 +8844,25 @@
       <c r="Q151" s="2">
         <v>18</v>
       </c>
-      <c r="S151" t="s">
+      <c r="R151" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="152" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A152" s="4">
         <v>43981</v>
       </c>
       <c r="B152" s="4">
-        <v>44667</v>
-      </c>
-      <c r="C152" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C152" s="17">
         <f t="shared" si="4"/>
-        <v>686</v>
+        <v>536</v>
       </c>
       <c r="D152" t="s">
         <v>10</v>
       </c>
-      <c r="E152" s="17">
+      <c r="E152" s="14">
         <v>1215</v>
       </c>
       <c r="F152" t="s">
@@ -8892,25 +8894,25 @@
       <c r="Q152" s="2">
         <v>31.4</v>
       </c>
-      <c r="S152" t="s">
+      <c r="R152" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="153" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A153" s="4">
         <v>43965</v>
       </c>
       <c r="B153" s="4">
-        <v>44668</v>
-      </c>
-      <c r="C153" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C153" s="17">
         <f t="shared" si="4"/>
-        <v>703</v>
+        <v>552</v>
       </c>
       <c r="D153" t="s">
         <v>2</v>
       </c>
-      <c r="E153" s="17">
+      <c r="E153" s="14">
         <v>706</v>
       </c>
       <c r="F153" t="s">
@@ -8941,21 +8943,21 @@
         <v>66</v>
       </c>
     </row>
-    <row r="154" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A154" s="4">
         <v>43963</v>
       </c>
       <c r="B154" s="4">
-        <v>44669</v>
-      </c>
-      <c r="C154" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C154" s="17">
         <f t="shared" si="4"/>
-        <v>706</v>
+        <v>554</v>
       </c>
       <c r="D154" t="s">
         <v>10</v>
       </c>
-      <c r="E154" s="17">
+      <c r="E154" s="14">
         <v>1209</v>
       </c>
       <c r="F154" t="s">
@@ -8989,25 +8991,25 @@
       <c r="Q154" s="2">
         <v>40.299999999999997</v>
       </c>
-      <c r="S154" t="s">
+      <c r="R154" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="155" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A155" s="4">
         <v>43955</v>
       </c>
       <c r="B155" s="4">
-        <v>44670</v>
-      </c>
-      <c r="C155" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C155" s="17">
         <f t="shared" si="4"/>
-        <v>715</v>
+        <v>562</v>
       </c>
       <c r="D155" t="s">
         <v>9</v>
       </c>
-      <c r="E155" s="17">
+      <c r="E155" s="14">
         <v>800</v>
       </c>
       <c r="F155" t="s">
@@ -9037,25 +9039,25 @@
       <c r="Q155" s="2">
         <v>17</v>
       </c>
-      <c r="S155" t="s">
+      <c r="R155" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="156" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
         <v>43949</v>
       </c>
       <c r="B156" s="4">
-        <v>44671</v>
-      </c>
-      <c r="C156" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C156" s="17">
         <f t="shared" si="4"/>
-        <v>722</v>
+        <v>568</v>
       </c>
       <c r="D156" t="s">
         <v>10</v>
       </c>
-      <c r="E156" s="17">
+      <c r="E156" s="14">
         <v>1227</v>
       </c>
       <c r="F156" t="s">
@@ -9089,25 +9091,25 @@
       <c r="Q156" s="2">
         <v>33.6</v>
       </c>
-      <c r="S156" t="s">
+      <c r="R156" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="157" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A157" s="4">
         <v>43936</v>
       </c>
       <c r="B157" s="4">
-        <v>44672</v>
-      </c>
-      <c r="C157" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C157" s="17">
         <f t="shared" si="4"/>
-        <v>736</v>
+        <v>581</v>
       </c>
       <c r="D157" t="s">
         <v>10</v>
       </c>
-      <c r="E157" s="17">
+      <c r="E157" s="14">
         <v>1270</v>
       </c>
       <c r="F157" t="s">
@@ -9141,25 +9143,25 @@
       <c r="Q157" s="2">
         <v>36.1</v>
       </c>
-      <c r="S157" t="s">
+      <c r="R157" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A158" s="4">
         <v>43930</v>
       </c>
       <c r="B158" s="4">
-        <v>44673</v>
-      </c>
-      <c r="C158" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C158" s="17">
         <f t="shared" si="4"/>
-        <v>743</v>
+        <v>587</v>
       </c>
       <c r="D158" t="s">
         <v>2</v>
       </c>
-      <c r="E158" s="17">
+      <c r="E158" s="14">
         <v>709</v>
       </c>
       <c r="F158" t="s">
@@ -9189,25 +9191,25 @@
       <c r="Q158" s="2">
         <v>64</v>
       </c>
-      <c r="S158" t="s">
+      <c r="R158" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A159" s="4">
         <v>43920</v>
       </c>
       <c r="B159" s="4">
-        <v>44674</v>
-      </c>
-      <c r="C159" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C159" s="17">
         <f t="shared" si="4"/>
-        <v>754</v>
+        <v>597</v>
       </c>
       <c r="D159" t="s">
         <v>9</v>
       </c>
-      <c r="E159" s="17">
+      <c r="E159" s="14">
         <v>800</v>
       </c>
       <c r="F159" t="s">
@@ -9237,25 +9239,25 @@
       <c r="Q159" s="2">
         <v>18</v>
       </c>
-      <c r="S159" t="s">
+      <c r="R159" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="160" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A160" s="4">
         <v>43917</v>
       </c>
       <c r="B160" s="4">
-        <v>44675</v>
-      </c>
-      <c r="C160" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C160" s="17">
         <f t="shared" si="4"/>
-        <v>758</v>
+        <v>600</v>
       </c>
       <c r="D160" t="s">
         <v>10</v>
       </c>
-      <c r="E160" s="17">
+      <c r="E160" s="14">
         <v>1230</v>
       </c>
       <c r="F160" t="s">
@@ -9287,25 +9289,25 @@
       <c r="Q160" s="2">
         <v>37.299999999999997</v>
       </c>
-      <c r="S160" t="s">
+      <c r="R160" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="161" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A161" s="4">
         <v>43906</v>
       </c>
       <c r="B161" s="4">
-        <v>44676</v>
-      </c>
-      <c r="C161" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C161" s="17">
         <f t="shared" si="4"/>
-        <v>770</v>
+        <v>611</v>
       </c>
       <c r="D161" t="s">
         <v>7</v>
       </c>
-      <c r="E161" s="17">
+      <c r="E161" s="14">
         <v>1273</v>
       </c>
       <c r="F161" t="s">
@@ -9335,25 +9337,25 @@
       </c>
       <c r="P161" s="2"/>
       <c r="Q161" s="2"/>
-      <c r="S161" t="s">
+      <c r="R161" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="162" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A162" s="4">
         <v>43903</v>
       </c>
       <c r="B162" s="4">
-        <v>44677</v>
-      </c>
-      <c r="C162" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C162" s="17">
         <f t="shared" si="4"/>
-        <v>774</v>
+        <v>614</v>
       </c>
       <c r="D162" t="s">
         <v>2</v>
       </c>
-      <c r="E162" s="17">
+      <c r="E162" s="14">
         <v>702</v>
       </c>
       <c r="F162" t="s">
@@ -9383,25 +9385,25 @@
       <c r="Q162" s="2">
         <v>64</v>
       </c>
-      <c r="S162" t="s">
+      <c r="R162" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="163" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A163" s="4">
         <v>43902</v>
       </c>
       <c r="B163" s="4">
-        <v>44678</v>
-      </c>
-      <c r="C163" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C163" s="17">
         <f t="shared" si="4"/>
-        <v>776</v>
+        <v>615</v>
       </c>
       <c r="D163" t="s">
         <v>10</v>
       </c>
-      <c r="E163" s="17">
+      <c r="E163" s="14">
         <v>1135</v>
       </c>
       <c r="F163" t="s">
@@ -9433,25 +9435,25 @@
       <c r="Q163" s="2">
         <v>34.200000000000003</v>
       </c>
-      <c r="S163" t="s">
+      <c r="R163" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="164" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A164" s="4">
         <v>43890</v>
       </c>
       <c r="B164" s="4">
-        <v>44679</v>
-      </c>
-      <c r="C164" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C164" s="17">
         <f t="shared" si="4"/>
-        <v>789</v>
+        <v>627</v>
       </c>
       <c r="D164" t="s">
         <v>9</v>
       </c>
-      <c r="E164" s="17">
+      <c r="E164" s="14">
         <v>796</v>
       </c>
       <c r="F164" t="s">
@@ -9481,25 +9483,25 @@
       <c r="Q164" s="2">
         <v>18</v>
       </c>
-      <c r="S164" t="s">
+      <c r="R164" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="165" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A165" s="4">
         <v>43889</v>
       </c>
       <c r="B165" s="4">
-        <v>44680</v>
-      </c>
-      <c r="C165" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C165" s="17">
         <f t="shared" si="4"/>
-        <v>791</v>
+        <v>628</v>
       </c>
       <c r="D165" t="s">
         <v>10</v>
       </c>
-      <c r="E165" s="17">
+      <c r="E165" s="14">
         <v>1043</v>
       </c>
       <c r="F165" t="s">
@@ -9531,25 +9533,25 @@
       <c r="Q165" s="2">
         <v>38.299999999999997</v>
       </c>
-      <c r="S165" t="s">
+      <c r="R165" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="166" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A166" s="4">
         <v>43879</v>
       </c>
       <c r="B166" s="4">
-        <v>44681</v>
-      </c>
-      <c r="C166" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C166" s="17">
         <f t="shared" si="4"/>
-        <v>802</v>
+        <v>638</v>
       </c>
       <c r="D166" t="s">
         <v>7</v>
       </c>
-      <c r="E166" s="17">
+      <c r="E166" s="14">
         <v>1445</v>
       </c>
       <c r="F166" t="s">
@@ -9579,25 +9581,25 @@
       </c>
       <c r="P166" s="2"/>
       <c r="Q166" s="2"/>
-      <c r="S166" t="s">
+      <c r="R166" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="167" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
         <v>43875</v>
       </c>
       <c r="B167" s="4">
-        <v>44682</v>
-      </c>
-      <c r="C167" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C167" s="17">
         <f t="shared" si="4"/>
-        <v>807</v>
+        <v>642</v>
       </c>
       <c r="D167" t="s">
         <v>2</v>
       </c>
-      <c r="E167" s="17">
+      <c r="E167" s="14">
         <v>705</v>
       </c>
       <c r="F167" t="s">
@@ -9627,25 +9629,25 @@
       <c r="Q167" s="2">
         <v>62</v>
       </c>
-      <c r="S167" t="s">
+      <c r="R167" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="168" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A168" s="4">
         <v>43874</v>
       </c>
       <c r="B168" s="4">
-        <v>44683</v>
-      </c>
-      <c r="C168" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C168" s="17">
         <f t="shared" si="4"/>
-        <v>809</v>
+        <v>643</v>
       </c>
       <c r="D168" t="s">
         <v>10</v>
       </c>
-      <c r="E168" s="17">
+      <c r="E168" s="14">
         <v>1045</v>
       </c>
       <c r="F168" t="s">
@@ -9677,25 +9679,25 @@
       <c r="Q168" s="2">
         <v>37.700000000000003</v>
       </c>
-      <c r="S168" t="s">
+      <c r="R168" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="169" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A169" s="4">
         <v>43860</v>
       </c>
       <c r="B169" s="4">
-        <v>44684</v>
-      </c>
-      <c r="C169" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C169" s="17">
         <f t="shared" si="4"/>
-        <v>824</v>
+        <v>657</v>
       </c>
       <c r="D169" t="s">
         <v>10</v>
       </c>
-      <c r="E169" s="17">
+      <c r="E169" s="14">
         <v>975</v>
       </c>
       <c r="F169" t="s">
@@ -9727,25 +9729,25 @@
       <c r="Q169" s="2">
         <v>29</v>
       </c>
-      <c r="S169" t="s">
+      <c r="R169" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="170" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A170" s="4">
         <v>43858</v>
       </c>
       <c r="B170" s="4">
-        <v>44685</v>
-      </c>
-      <c r="C170" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C170" s="17">
         <f t="shared" si="4"/>
-        <v>827</v>
+        <v>659</v>
       </c>
       <c r="D170" t="s">
         <v>9</v>
       </c>
-      <c r="E170" s="17">
+      <c r="E170" s="14">
         <v>806</v>
       </c>
       <c r="F170" t="s">
@@ -9777,25 +9779,25 @@
       <c r="Q170" s="2">
         <v>24</v>
       </c>
-      <c r="S170" t="s">
+      <c r="R170" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="171" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A171" s="4">
         <v>43847</v>
       </c>
       <c r="B171" s="4">
-        <v>44686</v>
-      </c>
-      <c r="C171" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C171" s="17">
         <f t="shared" si="4"/>
-        <v>839</v>
+        <v>670</v>
       </c>
       <c r="D171" t="s">
         <v>2</v>
       </c>
-      <c r="E171" s="17">
+      <c r="E171" s="14">
         <v>709</v>
       </c>
       <c r="F171" t="s">
@@ -9825,25 +9827,25 @@
       <c r="Q171" s="2">
         <v>63</v>
       </c>
-      <c r="S171" t="s">
+      <c r="R171" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="172" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A172" s="4">
         <v>43846</v>
       </c>
       <c r="B172" s="4">
-        <v>44687</v>
-      </c>
-      <c r="C172" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C172" s="17">
         <f t="shared" si="4"/>
-        <v>841</v>
+        <v>671</v>
       </c>
       <c r="D172" t="s">
         <v>10</v>
       </c>
-      <c r="E172" s="17">
+      <c r="E172" s="14">
         <v>950</v>
       </c>
       <c r="F172" t="s">
@@ -9875,25 +9877,25 @@
       <c r="Q172" s="2">
         <v>34.5</v>
       </c>
-      <c r="S172" t="s">
+      <c r="R172" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="173" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A173" s="4">
         <v>43829</v>
       </c>
       <c r="B173" s="4">
-        <v>44688</v>
-      </c>
-      <c r="C173" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C173" s="17">
         <f t="shared" si="4"/>
-        <v>859</v>
+        <v>688</v>
       </c>
       <c r="D173" t="s">
         <v>9</v>
       </c>
-      <c r="E173" s="17">
+      <c r="E173" s="14">
         <v>951</v>
       </c>
       <c r="F173" t="s">
@@ -9923,25 +9925,25 @@
       <c r="Q173" s="2">
         <v>15</v>
       </c>
-      <c r="S173" t="s">
+      <c r="R173" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="174" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A174" s="4">
         <v>43825</v>
       </c>
       <c r="B174" s="4">
-        <v>44689</v>
-      </c>
-      <c r="C174" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C174" s="17">
         <f t="shared" si="4"/>
-        <v>864</v>
+        <v>692</v>
       </c>
       <c r="D174" t="s">
         <v>10</v>
       </c>
-      <c r="E174" s="17">
+      <c r="E174" s="14">
         <v>1030</v>
       </c>
       <c r="F174" t="s">
@@ -9973,25 +9975,25 @@
       <c r="Q174" s="2">
         <v>31.1</v>
       </c>
-      <c r="S174" t="s">
+      <c r="R174" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="175" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A175" s="4">
         <v>43819</v>
       </c>
       <c r="B175" s="4">
-        <v>44690</v>
-      </c>
-      <c r="C175" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C175" s="17">
         <f t="shared" si="4"/>
-        <v>871</v>
+        <v>698</v>
       </c>
       <c r="D175" t="s">
         <v>2</v>
       </c>
-      <c r="E175" s="17">
+      <c r="E175" s="14">
         <v>702</v>
       </c>
       <c r="F175" t="s">
@@ -10021,25 +10023,25 @@
       <c r="Q175" s="2">
         <v>59</v>
       </c>
-      <c r="S175" t="s">
+      <c r="R175" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="176" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A176" s="4">
         <v>43798</v>
       </c>
       <c r="B176" s="4">
-        <v>44691</v>
-      </c>
-      <c r="C176" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C176" s="17">
         <f t="shared" si="4"/>
-        <v>893</v>
+        <v>719</v>
       </c>
       <c r="D176" t="s">
         <v>2</v>
       </c>
-      <c r="E176" s="17">
+      <c r="E176" s="14">
         <v>708</v>
       </c>
       <c r="F176" t="s">
@@ -10069,25 +10071,25 @@
       <c r="Q176" s="2">
         <v>58</v>
       </c>
-      <c r="S176" t="s">
+      <c r="R176" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="177" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A177" s="4">
         <v>43795</v>
       </c>
       <c r="B177" s="4">
-        <v>44692</v>
-      </c>
-      <c r="C177" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C177" s="17">
         <f t="shared" si="4"/>
-        <v>897</v>
+        <v>722</v>
       </c>
       <c r="D177" t="s">
         <v>10</v>
       </c>
-      <c r="E177" s="17">
+      <c r="E177" s="14">
         <v>1159</v>
       </c>
       <c r="F177" t="s">
@@ -10119,25 +10121,25 @@
       <c r="Q177" s="2">
         <v>33.6</v>
       </c>
-      <c r="S177" t="s">
+      <c r="R177" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="178" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
         <v>43795</v>
       </c>
       <c r="B178" s="4">
-        <v>44693</v>
-      </c>
-      <c r="C178" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C178" s="17">
         <f t="shared" si="4"/>
-        <v>898</v>
+        <v>722</v>
       </c>
       <c r="D178" t="s">
         <v>9</v>
       </c>
-      <c r="E178" s="17">
+      <c r="E178" s="14">
         <v>1014</v>
       </c>
       <c r="F178" t="s">
@@ -10167,25 +10169,25 @@
       <c r="Q178" s="2">
         <v>25</v>
       </c>
-      <c r="S178" t="s">
+      <c r="R178" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="179" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A179" s="4">
         <v>43768</v>
       </c>
       <c r="B179" s="4">
-        <v>44694</v>
-      </c>
-      <c r="C179" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C179" s="17">
         <f t="shared" si="4"/>
-        <v>926</v>
+        <v>749</v>
       </c>
       <c r="D179" t="s">
         <v>10</v>
       </c>
-      <c r="E179" s="17">
+      <c r="E179" s="14">
         <v>1304</v>
       </c>
       <c r="F179" t="s">
@@ -10217,25 +10219,25 @@
       <c r="Q179" s="2">
         <v>29.1</v>
       </c>
-      <c r="S179" t="s">
+      <c r="R179" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="180" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A180" s="4">
         <v>43768</v>
       </c>
       <c r="B180" s="4">
-        <v>44695</v>
-      </c>
-      <c r="C180" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C180" s="17">
         <f t="shared" si="4"/>
-        <v>927</v>
+        <v>749</v>
       </c>
       <c r="D180" t="s">
         <v>2</v>
       </c>
-      <c r="E180" s="17">
+      <c r="E180" s="14">
         <v>708</v>
       </c>
       <c r="F180" t="s">
@@ -10265,25 +10267,25 @@
       <c r="Q180" s="2">
         <v>57</v>
       </c>
-      <c r="S180" t="s">
+      <c r="R180" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="181" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A181" s="4">
         <v>43767</v>
       </c>
       <c r="B181" s="4">
-        <v>44696</v>
-      </c>
-      <c r="C181" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C181" s="17">
         <f t="shared" si="4"/>
-        <v>929</v>
+        <v>750</v>
       </c>
       <c r="D181" t="s">
         <v>9</v>
       </c>
-      <c r="E181" s="17">
+      <c r="E181" s="14">
         <v>1005</v>
       </c>
       <c r="F181" t="s">
@@ -10313,25 +10315,25 @@
       <c r="Q181" s="2">
         <v>25</v>
       </c>
-      <c r="S181" t="s">
+      <c r="R181" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="182" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A182" s="4">
         <v>43749</v>
       </c>
       <c r="B182" s="4">
-        <v>44697</v>
-      </c>
-      <c r="C182" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C182" s="17">
         <f t="shared" si="4"/>
-        <v>948</v>
+        <v>768</v>
       </c>
       <c r="D182" t="s">
         <v>2</v>
       </c>
-      <c r="E182" s="17">
+      <c r="E182" s="14">
         <v>706</v>
       </c>
       <c r="F182" t="s">
@@ -10359,25 +10361,25 @@
       <c r="Q182" s="2">
         <v>52</v>
       </c>
-      <c r="S182" t="s">
+      <c r="R182" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="183" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A183" s="4">
         <v>43738</v>
       </c>
       <c r="B183" s="4">
-        <v>44698</v>
-      </c>
-      <c r="C183" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C183" s="17">
         <f t="shared" si="4"/>
-        <v>960</v>
+        <v>779</v>
       </c>
       <c r="D183" t="s">
         <v>9</v>
       </c>
-      <c r="E183" s="17">
+      <c r="E183" s="14">
         <v>827</v>
       </c>
       <c r="F183" t="s">
@@ -10407,25 +10409,25 @@
       <c r="Q183" s="2">
         <v>8</v>
       </c>
-      <c r="S183" t="s">
+      <c r="R183" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="184" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A184" s="4">
         <v>43733</v>
       </c>
       <c r="B184" s="4">
-        <v>44699</v>
-      </c>
-      <c r="C184" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C184" s="17">
         <f t="shared" si="4"/>
-        <v>966</v>
+        <v>784</v>
       </c>
       <c r="D184" t="s">
         <v>10</v>
       </c>
-      <c r="E184" s="17">
+      <c r="E184" s="14">
         <v>1061</v>
       </c>
       <c r="F184" t="s">
@@ -10457,25 +10459,25 @@
       <c r="Q184" s="2">
         <v>27.8</v>
       </c>
-      <c r="S184" t="s">
+      <c r="R184" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="185" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A185" s="4">
         <v>43707</v>
       </c>
       <c r="B185" s="4">
-        <v>44700</v>
-      </c>
-      <c r="C185" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C185" s="17">
         <f t="shared" si="4"/>
-        <v>993</v>
+        <v>810</v>
       </c>
       <c r="D185" t="s">
         <v>9</v>
       </c>
-      <c r="E185" s="17">
+      <c r="E185" s="14">
         <v>907</v>
       </c>
       <c r="F185" t="s">
@@ -10505,25 +10507,25 @@
       <c r="Q185" s="2">
         <v>20</v>
       </c>
-      <c r="S185" t="s">
+      <c r="R185" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="186" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A186" s="4">
         <v>43706</v>
       </c>
       <c r="B186" s="4">
-        <v>44701</v>
-      </c>
-      <c r="C186" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C186" s="17">
         <f t="shared" si="4"/>
-        <v>995</v>
+        <v>811</v>
       </c>
       <c r="D186" t="s">
         <v>10</v>
       </c>
-      <c r="E186" s="17">
+      <c r="E186" s="14">
         <v>1030</v>
       </c>
       <c r="F186" t="s">
@@ -10555,25 +10557,25 @@
       <c r="Q186" s="2">
         <v>24.4</v>
       </c>
-      <c r="S186" t="s">
+      <c r="R186" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="187" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A187" s="4">
         <v>43675</v>
       </c>
       <c r="B187" s="4">
-        <v>44702</v>
-      </c>
-      <c r="C187" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C187" s="17">
         <f t="shared" si="4"/>
-        <v>1027</v>
+        <v>842</v>
       </c>
       <c r="D187" t="s">
         <v>9</v>
       </c>
-      <c r="E187" s="17">
+      <c r="E187" s="14">
         <v>795</v>
       </c>
       <c r="F187" t="s">
@@ -10603,25 +10605,25 @@
       <c r="Q187" s="2">
         <v>14</v>
       </c>
-      <c r="S187" t="s">
+      <c r="R187" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="188" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A188" s="4">
         <v>43671</v>
       </c>
       <c r="B188" s="4">
-        <v>44703</v>
-      </c>
-      <c r="C188" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C188" s="17">
         <f t="shared" si="4"/>
-        <v>1032</v>
+        <v>846</v>
       </c>
       <c r="D188" t="s">
         <v>10</v>
       </c>
-      <c r="E188" s="17">
+      <c r="E188" s="14">
         <v>1017</v>
       </c>
       <c r="F188" t="s">
@@ -10653,25 +10655,25 @@
       <c r="Q188" s="2">
         <v>25.1</v>
       </c>
-      <c r="S188" t="s">
+      <c r="R188" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="189" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
         <v>43658</v>
       </c>
       <c r="B189" s="4">
-        <v>44704</v>
-      </c>
-      <c r="C189" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C189" s="17">
         <f t="shared" si="4"/>
-        <v>1046</v>
+        <v>859</v>
       </c>
       <c r="D189" t="s">
         <v>2</v>
       </c>
-      <c r="E189" s="17">
+      <c r="E189" s="14">
         <v>710</v>
       </c>
       <c r="F189" t="s">
@@ -10699,25 +10701,25 @@
       <c r="Q189" s="2">
         <v>50</v>
       </c>
-      <c r="S189" t="s">
+      <c r="R189" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="190" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A190" s="4">
         <v>43647</v>
       </c>
       <c r="B190" s="4">
-        <v>44705</v>
-      </c>
-      <c r="C190" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C190" s="17">
         <f t="shared" si="4"/>
-        <v>1058</v>
+        <v>870</v>
       </c>
       <c r="D190" t="s">
         <v>10</v>
       </c>
-      <c r="E190" s="17">
+      <c r="E190" s="14">
         <v>1005</v>
       </c>
       <c r="F190" t="s">
@@ -10749,25 +10751,25 @@
       <c r="Q190" s="2">
         <v>23.5</v>
       </c>
-      <c r="S190" t="s">
+      <c r="R190" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="191" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A191" s="4">
         <v>43640</v>
       </c>
       <c r="B191" s="4">
-        <v>44706</v>
-      </c>
-      <c r="C191" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C191" s="17">
         <f t="shared" si="4"/>
-        <v>1066</v>
+        <v>877</v>
       </c>
       <c r="D191" t="s">
         <v>9</v>
       </c>
-      <c r="E191" s="17">
+      <c r="E191" s="14">
         <v>804</v>
       </c>
       <c r="F191" t="s">
@@ -10797,25 +10799,25 @@
       <c r="Q191" s="2">
         <v>18</v>
       </c>
-      <c r="S191" t="s">
+      <c r="R191" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="192" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A192" s="4">
         <v>43619</v>
       </c>
       <c r="B192" s="4">
-        <v>44707</v>
-      </c>
-      <c r="C192" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C192" s="17">
         <f t="shared" si="4"/>
-        <v>1088</v>
+        <v>898</v>
       </c>
       <c r="D192" t="s">
         <v>9</v>
       </c>
-      <c r="E192" s="17">
+      <c r="E192" s="14">
         <v>803</v>
       </c>
       <c r="F192" t="s">
@@ -10845,25 +10847,25 @@
       <c r="Q192" s="2">
         <v>18</v>
       </c>
-      <c r="S192" t="s">
+      <c r="R192" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="193" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A193" s="4">
         <v>43616</v>
       </c>
       <c r="B193" s="4">
-        <v>44708</v>
-      </c>
-      <c r="C193" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C193" s="17">
         <f t="shared" si="4"/>
-        <v>1092</v>
+        <v>901</v>
       </c>
       <c r="D193" t="s">
         <v>10</v>
       </c>
-      <c r="E193" s="17">
+      <c r="E193" s="14">
         <v>1039</v>
       </c>
       <c r="F193" t="s">
@@ -10895,25 +10897,25 @@
       <c r="Q193" s="2">
         <v>22.7</v>
       </c>
-      <c r="S193" t="s">
+      <c r="R193" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="194" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A194" s="4">
         <v>43587</v>
       </c>
       <c r="B194" s="4">
-        <v>44709</v>
-      </c>
-      <c r="C194" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C194" s="17">
         <f t="shared" si="4"/>
-        <v>1122</v>
+        <v>930</v>
       </c>
       <c r="D194" t="s">
         <v>10</v>
       </c>
-      <c r="E194" s="17">
+      <c r="E194" s="14">
         <v>1039</v>
       </c>
       <c r="F194" t="s">
@@ -10945,25 +10947,25 @@
       <c r="Q194" s="2">
         <v>22.9</v>
       </c>
-      <c r="S194" t="s">
+      <c r="R194" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="195" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A195" s="4">
         <v>43583</v>
       </c>
       <c r="B195" s="4">
-        <v>44710</v>
-      </c>
-      <c r="C195" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C195" s="17">
         <f t="shared" ref="C195:C210" si="6">B195-A195</f>
-        <v>1127</v>
+        <v>934</v>
       </c>
       <c r="D195" t="s">
         <v>9</v>
       </c>
-      <c r="E195" s="17">
+      <c r="E195" s="14">
         <v>830</v>
       </c>
       <c r="F195" t="s">
@@ -10976,7 +10978,7 @@
         <v>0</v>
       </c>
       <c r="I195" s="11">
-        <f t="shared" ref="I195:I210" si="7">28-J195</f>
+        <f t="shared" ref="I195:I210" si="7">ABS(28-J195)</f>
         <v>18</v>
       </c>
       <c r="J195" s="2">
@@ -10993,25 +10995,25 @@
       <c r="Q195" s="2">
         <v>21</v>
       </c>
-      <c r="S195" t="s">
+      <c r="R195" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="196" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A196" s="4">
         <v>43555</v>
       </c>
       <c r="B196" s="4">
-        <v>44711</v>
-      </c>
-      <c r="C196" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C196" s="17">
         <f t="shared" si="6"/>
-        <v>1156</v>
+        <v>962</v>
       </c>
       <c r="D196" t="s">
         <v>10</v>
       </c>
-      <c r="E196" s="17">
+      <c r="E196" s="14">
         <v>1015</v>
       </c>
       <c r="F196" t="s">
@@ -11043,25 +11045,25 @@
       <c r="Q196" s="2">
         <v>24.8</v>
       </c>
-      <c r="S196" t="s">
+      <c r="R196" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="197" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A197" s="4">
         <v>43555</v>
       </c>
       <c r="B197" s="4">
-        <v>44712</v>
-      </c>
-      <c r="C197" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C197" s="17">
         <f t="shared" si="6"/>
-        <v>1157</v>
+        <v>962</v>
       </c>
       <c r="D197" t="s">
         <v>9</v>
       </c>
-      <c r="E197" s="17">
+      <c r="E197" s="14">
         <v>899</v>
       </c>
       <c r="F197" t="s">
@@ -11089,25 +11091,25 @@
       <c r="Q197" s="2">
         <v>21</v>
       </c>
-      <c r="S197" t="s">
+      <c r="R197" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="198" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A198" s="4">
         <v>43525</v>
       </c>
       <c r="B198" s="4">
-        <v>44713</v>
-      </c>
-      <c r="C198" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C198" s="17">
         <f t="shared" si="6"/>
-        <v>1188</v>
+        <v>992</v>
       </c>
       <c r="D198" t="s">
         <v>10</v>
       </c>
-      <c r="E198" s="17">
+      <c r="E198" s="14">
         <v>1001</v>
       </c>
       <c r="F198" t="s">
@@ -11139,25 +11141,25 @@
       <c r="Q198" s="2">
         <v>22.9</v>
       </c>
-      <c r="S198" t="s">
+      <c r="R198" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="199" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A199" s="4">
         <v>43524</v>
       </c>
       <c r="B199" s="4">
-        <v>44714</v>
-      </c>
-      <c r="C199" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C199" s="17">
         <f t="shared" si="6"/>
-        <v>1190</v>
+        <v>993</v>
       </c>
       <c r="D199" t="s">
         <v>9</v>
       </c>
-      <c r="E199" s="17">
+      <c r="E199" s="14">
         <v>801</v>
       </c>
       <c r="F199" t="s">
@@ -11187,25 +11189,25 @@
       <c r="Q199" s="2">
         <v>19</v>
       </c>
-      <c r="S199" t="s">
+      <c r="R199" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="200" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
         <v>43496</v>
       </c>
       <c r="B200" s="4">
-        <v>44715</v>
-      </c>
-      <c r="C200" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C200" s="17">
         <f t="shared" si="6"/>
-        <v>1219</v>
+        <v>1021</v>
       </c>
       <c r="D200" t="s">
         <v>10</v>
       </c>
-      <c r="E200" s="17">
+      <c r="E200" s="14">
         <v>1001</v>
       </c>
       <c r="F200" t="s">
@@ -11237,25 +11239,25 @@
       <c r="Q200" s="2">
         <v>28.7</v>
       </c>
-      <c r="S200" t="s">
+      <c r="R200" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="201" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A201" s="4">
         <v>43496</v>
       </c>
       <c r="B201" s="4">
-        <v>44716</v>
-      </c>
-      <c r="C201" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C201" s="17">
         <f t="shared" si="6"/>
-        <v>1220</v>
+        <v>1021</v>
       </c>
       <c r="D201" t="s">
         <v>9</v>
       </c>
-      <c r="E201" s="17">
+      <c r="E201" s="14">
         <v>800</v>
       </c>
       <c r="F201" t="s">
@@ -11285,25 +11287,25 @@
       <c r="Q201" s="2">
         <v>28</v>
       </c>
-      <c r="S201" t="s">
+      <c r="R201" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="202" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A202" s="4">
         <v>43476</v>
       </c>
       <c r="B202" s="4">
-        <v>44717</v>
-      </c>
-      <c r="C202" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C202" s="17">
         <f t="shared" si="6"/>
-        <v>1241</v>
+        <v>1041</v>
       </c>
       <c r="D202" t="s">
         <v>2</v>
       </c>
-      <c r="E202" s="17">
+      <c r="E202" s="14">
         <v>704</v>
       </c>
       <c r="F202" t="s">
@@ -11333,25 +11335,25 @@
       <c r="Q202" s="2">
         <v>49</v>
       </c>
-      <c r="S202" t="s">
+      <c r="R202" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="203" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A203" s="4">
         <v>43462</v>
       </c>
       <c r="B203" s="4">
-        <v>44718</v>
-      </c>
-      <c r="C203" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C203" s="17">
         <f t="shared" si="6"/>
-        <v>1256</v>
+        <v>1055</v>
       </c>
       <c r="D203" t="s">
         <v>9</v>
       </c>
-      <c r="E203" s="17">
+      <c r="E203" s="14">
         <v>800</v>
       </c>
       <c r="F203" t="s">
@@ -11381,25 +11383,25 @@
       <c r="Q203" s="2">
         <v>28</v>
       </c>
-      <c r="S203" t="s">
+      <c r="R203" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="204" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A204" s="4">
         <v>43434</v>
       </c>
       <c r="B204" s="4">
-        <v>44719</v>
-      </c>
-      <c r="C204" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C204" s="17">
         <f t="shared" si="6"/>
-        <v>1285</v>
+        <v>1083</v>
       </c>
       <c r="D204" t="s">
         <v>9</v>
       </c>
-      <c r="E204" s="17">
+      <c r="E204" s="14">
         <v>800</v>
       </c>
       <c r="F204" t="s">
@@ -11427,25 +11429,25 @@
       </c>
       <c r="P204" s="2"/>
       <c r="Q204" s="2"/>
-      <c r="S204" t="s">
+      <c r="R204" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="205" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A205" s="4">
         <v>43407</v>
       </c>
       <c r="B205" s="4">
-        <v>44720</v>
-      </c>
-      <c r="C205" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C205" s="17">
         <f t="shared" si="6"/>
-        <v>1313</v>
+        <v>1110</v>
       </c>
       <c r="D205" t="s">
         <v>9</v>
       </c>
-      <c r="E205" s="17">
+      <c r="E205" s="14">
         <v>800</v>
       </c>
       <c r="F205" t="s">
@@ -11473,25 +11475,25 @@
       </c>
       <c r="P205" s="2"/>
       <c r="Q205" s="2"/>
-      <c r="S205" t="s">
+      <c r="R205" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="206" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A206" s="4">
         <v>43375</v>
       </c>
       <c r="B206" s="4">
-        <v>44721</v>
-      </c>
-      <c r="C206" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C206" s="17">
         <f t="shared" si="6"/>
-        <v>1346</v>
+        <v>1142</v>
       </c>
       <c r="D206" t="s">
         <v>9</v>
       </c>
-      <c r="E206" s="17">
+      <c r="E206" s="14">
         <v>752</v>
       </c>
       <c r="F206" t="s">
@@ -11519,25 +11521,25 @@
       </c>
       <c r="P206" s="2"/>
       <c r="Q206" s="2"/>
-      <c r="S206" t="s">
+      <c r="R206" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="207" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A207" s="4">
         <v>43343</v>
       </c>
       <c r="B207" s="4">
-        <v>44722</v>
-      </c>
-      <c r="C207" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C207" s="17">
         <f t="shared" si="6"/>
-        <v>1379</v>
+        <v>1174</v>
       </c>
       <c r="D207" t="s">
         <v>9</v>
       </c>
-      <c r="E207" s="17">
+      <c r="E207" s="14">
         <v>800</v>
       </c>
       <c r="F207" t="s">
@@ -11565,25 +11567,25 @@
       </c>
       <c r="P207" s="2"/>
       <c r="Q207" s="2"/>
-      <c r="S207" t="s">
+      <c r="R207" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="208" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A208" s="4">
         <v>43311</v>
       </c>
       <c r="B208" s="4">
-        <v>44723</v>
-      </c>
-      <c r="C208" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C208" s="17">
         <f t="shared" si="6"/>
-        <v>1412</v>
+        <v>1206</v>
       </c>
       <c r="D208" t="s">
         <v>9</v>
       </c>
-      <c r="E208" s="17">
+      <c r="E208" s="14">
         <v>800</v>
       </c>
       <c r="F208" t="s">
@@ -11611,25 +11613,25 @@
       </c>
       <c r="P208" s="2"/>
       <c r="Q208" s="2"/>
-      <c r="S208" t="s">
+      <c r="R208" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="209" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A209" s="4">
         <v>43279</v>
       </c>
       <c r="B209" s="4">
-        <v>44724</v>
-      </c>
-      <c r="C209" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C209" s="17">
         <f t="shared" si="6"/>
-        <v>1445</v>
+        <v>1238</v>
       </c>
       <c r="D209" t="s">
         <v>9</v>
       </c>
-      <c r="E209" s="17">
+      <c r="E209" s="14">
         <v>927</v>
       </c>
       <c r="F209" t="s">
@@ -11657,25 +11659,25 @@
       </c>
       <c r="P209" s="2"/>
       <c r="Q209" s="2"/>
-      <c r="S209" t="s">
+      <c r="R209" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="210" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A210" s="4">
         <v>43243</v>
       </c>
       <c r="B210" s="4">
-        <v>44725</v>
-      </c>
-      <c r="C210" s="14">
+        <v>44517</v>
+      </c>
+      <c r="C210" s="17">
         <f t="shared" si="6"/>
-        <v>1482</v>
+        <v>1274</v>
       </c>
       <c r="D210" t="s">
         <v>9</v>
       </c>
-      <c r="E210" s="17">
+      <c r="E210" s="14">
         <v>1573</v>
       </c>
       <c r="F210" t="s">
@@ -11703,13 +11705,13 @@
       </c>
       <c r="P210" s="2"/>
       <c r="Q210" s="2"/>
-      <c r="S210" t="s">
+      <c r="R210" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S1" xr:uid="{83B63D74-A7C5-D44D-829C-4061152A24B6}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S210">
+  <autoFilter ref="A1:R1" xr:uid="{83B63D74-A7C5-D44D-829C-4061152A24B6}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R210">
       <sortCondition descending="1" ref="A1:A210"/>
     </sortState>
   </autoFilter>
@@ -11753,93 +11755,243 @@
       <c r="C2" t="s">
         <v>87</v>
       </c>
+      <c r="D2">
+        <f>MIN(data!A2:A210)</f>
+        <v>43243</v>
+      </c>
+      <c r="E2">
+        <f>MAX(data!A2:A210)</f>
+        <v>44505</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>61</v>
       </c>
+      <c r="B3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3">
+        <f>MIN(data!B2:B210)</f>
+        <v>44517</v>
+      </c>
+      <c r="E3">
+        <f>MAX(data!B2:B210)</f>
+        <v>44517</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>60</v>
       </c>
+      <c r="B4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="18">
+        <f>MIN(data!C2:C210)</f>
+        <v>12</v>
+      </c>
+      <c r="E4" s="18">
+        <f>MAX(data!C2:C210)</f>
+        <v>1274</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>62</v>
       </c>
+      <c r="D5">
+        <f>MIN(data!D2:D210)</f>
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <f>MAX(data!D2:D210)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>63</v>
       </c>
+      <c r="D6">
+        <f>MIN(data!E2:E210)</f>
+        <v>100</v>
+      </c>
+      <c r="E6">
+        <f>MAX(data!E2:E210)</f>
+        <v>7613</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>64</v>
       </c>
+      <c r="D7">
+        <f>MIN(data!F2:F210)</f>
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <f>MAX(data!F2:F210)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>65</v>
       </c>
+      <c r="D8">
+        <f>MIN(data!G2:G210)</f>
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <f>MAX(data!G2:G210)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>54</v>
       </c>
+      <c r="D9">
+        <f>MIN(data!H2:H210)</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <f>MAX(data!H2:H210)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>59</v>
       </c>
+      <c r="D10" s="2">
+        <f>MIN(data!I2:I210)</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <f>MAX(data!I2:I210)</f>
+        <v>26</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="15" t="s">
         <v>66</v>
       </c>
+      <c r="D11" s="2">
+        <f>MIN(data!J2:J210)</f>
+        <v>2</v>
+      </c>
+      <c r="E11" s="2">
+        <f>MAX(data!J2:J210)</f>
+        <v>39</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="15" t="s">
         <v>67</v>
       </c>
+      <c r="D12" s="2">
+        <f>MIN(data!K2:K210)</f>
+        <v>0.5</v>
+      </c>
+      <c r="E12" s="2">
+        <f>MAX(data!K2:K210)</f>
+        <v>36</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="15" t="s">
         <v>68</v>
       </c>
+      <c r="D13" s="2">
+        <f>MIN(data!L2:L210)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <f>MAX(data!L2:L210)</f>
+        <v>35</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="15" t="s">
         <v>69</v>
       </c>
+      <c r="D14" s="2">
+        <f>MIN(data!M2:M210)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="2">
+        <f>MAX(data!M2:M210)</f>
+        <v>13</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="15" t="s">
         <v>70</v>
       </c>
+      <c r="D15" s="2">
+        <f>MIN(data!N2:N210)</f>
+        <v>2</v>
+      </c>
+      <c r="E15" s="2">
+        <f>MAX(data!N2:N210)</f>
+        <v>18</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="15" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" s="18" t="s">
+      <c r="D16" s="2">
+        <f>MIN(data!O2:O210)</f>
+        <v>0.4</v>
+      </c>
+      <c r="E16" s="2">
+        <f>MAX(data!O2:O210)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="15" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D17">
+        <f>MIN(data!A2:A210)</f>
+        <v>43243</v>
+      </c>
+      <c r="E17" s="2">
+        <f>MAX(data!P2:P210)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D18" s="2">
+        <f>MIN(data!P2:P210)</f>
+        <v>0.3</v>
+      </c>
+      <c r="E18" s="2">
+        <f>MAX(data!Q2:Q210)</f>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D19" s="2">
+        <f>MIN(data!Q2:Q210)</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="2" t="e">
+        <f>MAX(data!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>75</v>
       </c>
@@ -11852,32 +12004,47 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{840051B2-FA27-7349-A3AF-BAC66CCD6264}">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>85</v>
+      </c>
+      <c r="B5" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
